--- a/src/main/resources/uk/gov/hmcts/ccd/test_definitions/excel/CCD_CNP_RDM5118.xlsx
+++ b/src/main/resources/uk/gov/hmcts/ccd/test_definitions/excel/CCD_CNP_RDM5118.xlsx
@@ -53,7 +53,7 @@
     <t>DisplayOrder</t>
   </si>
   <si>
-    <t>AAT_AUTH_1</t>
+    <t>AAT_AUTH_15</t>
   </si>
   <si>
     <t>TextField</t>
@@ -62,25 +62,25 @@
     <t>Search `Text` field</t>
   </si>
   <si>
-    <t>AAT_AUTH_15</t>
+    <t>AAT_AUTH_8</t>
+  </si>
+  <si>
+    <t>AAT_AUTH_6</t>
+  </si>
+  <si>
+    <t>AAT_AUTH_1</t>
   </si>
   <si>
     <t>AAT_AUTH_2</t>
   </si>
   <si>
-    <t>AAT_AUTH_3</t>
+    <t>AAT_AUTH_5</t>
   </si>
   <si>
     <t>AAT_AUTH_4</t>
   </si>
   <si>
-    <t>AAT_AUTH_5</t>
-  </si>
-  <si>
-    <t>AAT_AUTH_6</t>
-  </si>
-  <si>
-    <t>AAT_AUTH_8</t>
+    <t>AAT_AUTH_3</t>
   </si>
   <si>
     <t>UserProfile</t>
@@ -293,6 +293,9 @@
     <t>Collection</t>
   </si>
   <si>
+    <t>CollectionPermissionField</t>
+  </si>
+  <si>
     <t>ComplexField</t>
   </si>
   <si>
@@ -315,6 +318,18 @@
   </si>
   <si>
     <t>AddressUK</t>
+  </si>
+  <si>
+    <t>AddressForeignField</t>
+  </si>
+  <si>
+    <t>A `AddressForeignField` field</t>
+  </si>
+  <si>
+    <t>RestoredComplexType</t>
+  </si>
+  <si>
+    <t>A `RestoredComplexType` field</t>
   </si>
   <si>
     <t>DocumentField</t>
@@ -354,21 +369,6 @@
   </si>
   <si>
     <t>CaseHistoryViewer</t>
-  </si>
-  <si>
-    <t>CollectionPermissionField</t>
-  </si>
-  <si>
-    <t>AddressForeignField</t>
-  </si>
-  <si>
-    <t>A `AddressForeignField` field</t>
-  </si>
-  <si>
-    <t>RestoredComplexType</t>
-  </si>
-  <si>
-    <t>A `RestoredComplexType` field</t>
   </si>
   <si>
     <t>ComplexTypes</t>
@@ -767,7 +767,7 @@
     <t>Demonstrate everything CCD can do!</t>
   </si>
   <si>
-    <t>http://host.docker.internal:5555/case_type/fe-functional-test/callback_get_case</t>
+    <t>${TEST_STUB_SERVICE_BASE_URL:http://ccd-test-stubs-service-aat.service.core-compute-aat.internal}/case_type/fe-functional-test/callback_get_case</t>
   </si>
   <si>
     <t>Demo case AAT_AUTH_3</t>
@@ -803,16 +803,22 @@
     <t>To do</t>
   </si>
   <si>
+    <t>CUSTOM  TITLE DISPLAY</t>
+  </si>
+  <si>
     <t>In progress</t>
   </si>
   <si>
     <t>Done</t>
   </si>
   <si>
-    <t>CUSTOM  TITLE DISPLAY</t>
+    <t>AuthorisationCaseType</t>
   </si>
   <si>
-    <t>AuthorisationCaseType</t>
+    <t>D</t>
+  </si>
+  <si>
+    <t>RU</t>
   </si>
   <si>
     <t>C</t>
@@ -821,16 +827,10 @@
     <t>R</t>
   </si>
   <si>
-    <t>CR</t>
-  </si>
-  <si>
     <t>U</t>
   </si>
   <si>
-    <t>RU</t>
-  </si>
-  <si>
-    <t>D</t>
+    <t>CR</t>
   </si>
 </sst>
 </file>
@@ -1242,7 +1242,7 @@
       </c>
       <c r="B12"/>
       <c r="C12" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="D12" t="s">
         <v>186</v>
@@ -1257,7 +1257,7 @@
       </c>
       <c r="B13"/>
       <c r="C13" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="D13" t="s">
         <v>188</v>
@@ -1272,7 +1272,7 @@
       </c>
       <c r="B14"/>
       <c r="C14" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="D14" t="s">
         <v>190</v>
@@ -3905,7 +3905,7 @@
         <v>7</v>
       </c>
       <c r="D15" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E15" t="s">
         <v>134</v>
@@ -3923,13 +3923,13 @@
         <v>7</v>
       </c>
       <c r="D16" t="s">
-        <v>83</v>
+        <v>96</v>
       </c>
       <c r="E16" t="s">
         <v>134</v>
       </c>
       <c r="F16" t="s">
-        <v>133</v>
+        <v>218</v>
       </c>
     </row>
     <row r="17">
@@ -3941,7 +3941,7 @@
         <v>7</v>
       </c>
       <c r="D17" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="E17" t="s">
         <v>134</v>
@@ -3959,13 +3959,13 @@
         <v>7</v>
       </c>
       <c r="D18" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="E18" t="s">
         <v>134</v>
       </c>
       <c r="F18" t="s">
-        <v>133</v>
+        <v>219</v>
       </c>
     </row>
     <row r="19">
@@ -3977,7 +3977,7 @@
         <v>7</v>
       </c>
       <c r="D19" t="s">
-        <v>99</v>
+        <v>88</v>
       </c>
       <c r="E19" t="s">
         <v>134</v>
@@ -3995,7 +3995,7 @@
         <v>7</v>
       </c>
       <c r="D20" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="E20" t="s">
         <v>134</v>
@@ -4013,10 +4013,10 @@
         <v>7</v>
       </c>
       <c r="D21" t="s">
-        <v>8</v>
+        <v>104</v>
       </c>
       <c r="E21" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F21" t="s">
         <v>133</v>
@@ -4031,10 +4031,10 @@
         <v>7</v>
       </c>
       <c r="D22" t="s">
-        <v>41</v>
+        <v>109</v>
       </c>
       <c r="E22" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F22" t="s">
         <v>133</v>
@@ -4049,7 +4049,7 @@
         <v>7</v>
       </c>
       <c r="D23" t="s">
-        <v>45</v>
+        <v>8</v>
       </c>
       <c r="E23" t="s">
         <v>135</v>
@@ -4067,7 +4067,7 @@
         <v>7</v>
       </c>
       <c r="D24" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="E24" t="s">
         <v>135</v>
@@ -4085,7 +4085,7 @@
         <v>7</v>
       </c>
       <c r="D25" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="E25" t="s">
         <v>135</v>
@@ -4103,7 +4103,7 @@
         <v>7</v>
       </c>
       <c r="D26" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="E26" t="s">
         <v>135</v>
@@ -4121,7 +4121,7 @@
         <v>7</v>
       </c>
       <c r="D27" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="E27" t="s">
         <v>135</v>
@@ -4139,7 +4139,7 @@
         <v>7</v>
       </c>
       <c r="D28" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="E28" t="s">
         <v>135</v>
@@ -4157,7 +4157,7 @@
         <v>7</v>
       </c>
       <c r="D29" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="E29" t="s">
         <v>135</v>
@@ -4175,7 +4175,7 @@
         <v>7</v>
       </c>
       <c r="D30" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="E30" t="s">
         <v>135</v>
@@ -4193,7 +4193,7 @@
         <v>7</v>
       </c>
       <c r="D31" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="E31" t="s">
         <v>135</v>
@@ -4211,7 +4211,7 @@
         <v>7</v>
       </c>
       <c r="D32" t="s">
-        <v>91</v>
+        <v>73</v>
       </c>
       <c r="E32" t="s">
         <v>135</v>
@@ -4229,7 +4229,7 @@
         <v>7</v>
       </c>
       <c r="D33" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="E33" t="s">
         <v>135</v>
@@ -4247,7 +4247,7 @@
         <v>7</v>
       </c>
       <c r="D34" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="E34" t="s">
         <v>135</v>
@@ -4265,7 +4265,7 @@
         <v>7</v>
       </c>
       <c r="D35" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E35" t="s">
         <v>135</v>
@@ -4283,10 +4283,10 @@
         <v>7</v>
       </c>
       <c r="D36" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E36" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F36" t="s">
         <v>133</v>
@@ -4301,7 +4301,7 @@
         <v>7</v>
       </c>
       <c r="D37" t="s">
-        <v>104</v>
+        <v>83</v>
       </c>
       <c r="E37" t="s">
         <v>135</v>
@@ -4316,13 +4316,13 @@
       </c>
       <c r="B38"/>
       <c r="C38" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D38" t="s">
-        <v>8</v>
+        <v>87</v>
       </c>
       <c r="E38" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F38" t="s">
         <v>133</v>
@@ -4334,13 +4334,13 @@
       </c>
       <c r="B39"/>
       <c r="C39" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D39" t="s">
-        <v>41</v>
+        <v>88</v>
       </c>
       <c r="E39" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F39" t="s">
         <v>133</v>
@@ -4352,13 +4352,13 @@
       </c>
       <c r="B40"/>
       <c r="C40" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D40" t="s">
-        <v>45</v>
+        <v>100</v>
       </c>
       <c r="E40" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F40" t="s">
         <v>133</v>
@@ -4370,13 +4370,13 @@
       </c>
       <c r="B41"/>
       <c r="C41" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D41" t="s">
-        <v>49</v>
+        <v>104</v>
       </c>
       <c r="E41" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F41" t="s">
         <v>133</v>
@@ -4388,13 +4388,13 @@
       </c>
       <c r="B42"/>
       <c r="C42" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D42" t="s">
-        <v>53</v>
+        <v>109</v>
       </c>
       <c r="E42" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F42" t="s">
         <v>133</v>
@@ -4409,7 +4409,7 @@
         <v>10</v>
       </c>
       <c r="D43" t="s">
-        <v>57</v>
+        <v>8</v>
       </c>
       <c r="E43" t="s">
         <v>134</v>
@@ -4427,7 +4427,7 @@
         <v>10</v>
       </c>
       <c r="D44" t="s">
-        <v>61</v>
+        <v>41</v>
       </c>
       <c r="E44" t="s">
         <v>134</v>
@@ -4445,7 +4445,7 @@
         <v>10</v>
       </c>
       <c r="D45" t="s">
-        <v>65</v>
+        <v>45</v>
       </c>
       <c r="E45" t="s">
         <v>134</v>
@@ -4463,7 +4463,7 @@
         <v>10</v>
       </c>
       <c r="D46" t="s">
-        <v>69</v>
+        <v>49</v>
       </c>
       <c r="E46" t="s">
         <v>134</v>
@@ -4481,7 +4481,7 @@
         <v>10</v>
       </c>
       <c r="D47" t="s">
-        <v>73</v>
+        <v>53</v>
       </c>
       <c r="E47" t="s">
         <v>134</v>
@@ -4499,7 +4499,7 @@
         <v>10</v>
       </c>
       <c r="D48" t="s">
-        <v>78</v>
+        <v>57</v>
       </c>
       <c r="E48" t="s">
         <v>134</v>
@@ -4517,7 +4517,7 @@
         <v>10</v>
       </c>
       <c r="D49" t="s">
-        <v>91</v>
+        <v>61</v>
       </c>
       <c r="E49" t="s">
         <v>134</v>
@@ -4535,13 +4535,13 @@
         <v>10</v>
       </c>
       <c r="D50" t="s">
-        <v>109</v>
+        <v>65</v>
       </c>
       <c r="E50" t="s">
         <v>134</v>
       </c>
       <c r="F50" t="s">
-        <v>218</v>
+        <v>133</v>
       </c>
     </row>
     <row r="51">
@@ -4553,7 +4553,7 @@
         <v>10</v>
       </c>
       <c r="D51" t="s">
-        <v>83</v>
+        <v>69</v>
       </c>
       <c r="E51" t="s">
         <v>134</v>
@@ -4571,13 +4571,13 @@
         <v>10</v>
       </c>
       <c r="D52" t="s">
-        <v>108</v>
+        <v>73</v>
       </c>
       <c r="E52" t="s">
         <v>134</v>
       </c>
       <c r="F52" t="s">
-        <v>219</v>
+        <v>133</v>
       </c>
     </row>
     <row r="53">
@@ -4589,7 +4589,7 @@
         <v>10</v>
       </c>
       <c r="D53" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="E53" t="s">
         <v>134</v>
@@ -4607,7 +4607,7 @@
         <v>10</v>
       </c>
       <c r="D54" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="E54" t="s">
         <v>134</v>
@@ -4625,7 +4625,7 @@
         <v>10</v>
       </c>
       <c r="D55" t="s">
-        <v>99</v>
+        <v>83</v>
       </c>
       <c r="E55" t="s">
         <v>134</v>
@@ -4643,7 +4643,7 @@
         <v>10</v>
       </c>
       <c r="D56" t="s">
-        <v>104</v>
+        <v>88</v>
       </c>
       <c r="E56" t="s">
         <v>134</v>
@@ -4661,10 +4661,10 @@
         <v>10</v>
       </c>
       <c r="D57" t="s">
-        <v>8</v>
+        <v>104</v>
       </c>
       <c r="E57" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F57" t="s">
         <v>133</v>
@@ -4679,10 +4679,10 @@
         <v>10</v>
       </c>
       <c r="D58" t="s">
-        <v>41</v>
+        <v>109</v>
       </c>
       <c r="E58" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F58" t="s">
         <v>133</v>
@@ -4697,7 +4697,7 @@
         <v>10</v>
       </c>
       <c r="D59" t="s">
-        <v>45</v>
+        <v>8</v>
       </c>
       <c r="E59" t="s">
         <v>135</v>
@@ -4715,7 +4715,7 @@
         <v>10</v>
       </c>
       <c r="D60" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="E60" t="s">
         <v>135</v>
@@ -4733,7 +4733,7 @@
         <v>10</v>
       </c>
       <c r="D61" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="E61" t="s">
         <v>135</v>
@@ -4751,7 +4751,7 @@
         <v>10</v>
       </c>
       <c r="D62" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="E62" t="s">
         <v>135</v>
@@ -4769,7 +4769,7 @@
         <v>10</v>
       </c>
       <c r="D63" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="E63" t="s">
         <v>135</v>
@@ -4787,7 +4787,7 @@
         <v>10</v>
       </c>
       <c r="D64" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="E64" t="s">
         <v>135</v>
@@ -4805,7 +4805,7 @@
         <v>10</v>
       </c>
       <c r="D65" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="E65" t="s">
         <v>135</v>
@@ -4823,7 +4823,7 @@
         <v>10</v>
       </c>
       <c r="D66" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="E66" t="s">
         <v>135</v>
@@ -4841,7 +4841,7 @@
         <v>10</v>
       </c>
       <c r="D67" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="E67" t="s">
         <v>135</v>
@@ -4859,7 +4859,7 @@
         <v>10</v>
       </c>
       <c r="D68" t="s">
-        <v>91</v>
+        <v>73</v>
       </c>
       <c r="E68" t="s">
         <v>135</v>
@@ -4877,7 +4877,7 @@
         <v>10</v>
       </c>
       <c r="D69" t="s">
-        <v>109</v>
+        <v>78</v>
       </c>
       <c r="E69" t="s">
         <v>135</v>
@@ -4895,10 +4895,10 @@
         <v>10</v>
       </c>
       <c r="D70" t="s">
-        <v>111</v>
+        <v>92</v>
       </c>
       <c r="E70" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F70" t="s">
         <v>133</v>
@@ -4931,7 +4931,7 @@
         <v>10</v>
       </c>
       <c r="D72" t="s">
-        <v>108</v>
+        <v>88</v>
       </c>
       <c r="E72" t="s">
         <v>135</v>
@@ -4949,7 +4949,7 @@
         <v>10</v>
       </c>
       <c r="D73" t="s">
-        <v>87</v>
+        <v>104</v>
       </c>
       <c r="E73" t="s">
         <v>135</v>
@@ -4967,7 +4967,7 @@
         <v>10</v>
       </c>
       <c r="D74" t="s">
-        <v>95</v>
+        <v>109</v>
       </c>
       <c r="E74" t="s">
         <v>135</v>
@@ -4982,13 +4982,13 @@
       </c>
       <c r="B75"/>
       <c r="C75" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D75" t="s">
-        <v>99</v>
+        <v>8</v>
       </c>
       <c r="E75" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F75" t="s">
         <v>133</v>
@@ -5000,13 +5000,13 @@
       </c>
       <c r="B76"/>
       <c r="C76" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D76" t="s">
-        <v>104</v>
+        <v>41</v>
       </c>
       <c r="E76" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F76" t="s">
         <v>133</v>
@@ -5021,7 +5021,7 @@
         <v>11</v>
       </c>
       <c r="D77" t="s">
-        <v>8</v>
+        <v>45</v>
       </c>
       <c r="E77" t="s">
         <v>134</v>
@@ -5039,7 +5039,7 @@
         <v>11</v>
       </c>
       <c r="D78" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="E78" t="s">
         <v>134</v>
@@ -5057,7 +5057,7 @@
         <v>11</v>
       </c>
       <c r="D79" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="E79" t="s">
         <v>134</v>
@@ -5075,7 +5075,7 @@
         <v>11</v>
       </c>
       <c r="D80" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="E80" t="s">
         <v>134</v>
@@ -5093,7 +5093,7 @@
         <v>11</v>
       </c>
       <c r="D81" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="E81" t="s">
         <v>134</v>
@@ -5111,7 +5111,7 @@
         <v>11</v>
       </c>
       <c r="D82" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="E82" t="s">
         <v>134</v>
@@ -5129,7 +5129,7 @@
         <v>11</v>
       </c>
       <c r="D83" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="E83" t="s">
         <v>134</v>
@@ -5147,7 +5147,7 @@
         <v>11</v>
       </c>
       <c r="D84" t="s">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="E84" t="s">
         <v>134</v>
@@ -5165,7 +5165,7 @@
         <v>11</v>
       </c>
       <c r="D85" t="s">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="E85" t="s">
         <v>134</v>
@@ -5183,7 +5183,7 @@
         <v>11</v>
       </c>
       <c r="D86" t="s">
-        <v>73</v>
+        <v>92</v>
       </c>
       <c r="E86" t="s">
         <v>134</v>
@@ -5201,7 +5201,7 @@
         <v>11</v>
       </c>
       <c r="D87" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="E87" t="s">
         <v>134</v>
@@ -5219,7 +5219,7 @@
         <v>11</v>
       </c>
       <c r="D88" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="E88" t="s">
         <v>134</v>
@@ -5237,7 +5237,7 @@
         <v>11</v>
       </c>
       <c r="D89" t="s">
-        <v>83</v>
+        <v>100</v>
       </c>
       <c r="E89" t="s">
         <v>134</v>
@@ -5255,7 +5255,7 @@
         <v>11</v>
       </c>
       <c r="D90" t="s">
-        <v>87</v>
+        <v>104</v>
       </c>
       <c r="E90" t="s">
         <v>134</v>
@@ -5273,7 +5273,7 @@
         <v>11</v>
       </c>
       <c r="D91" t="s">
-        <v>99</v>
+        <v>109</v>
       </c>
       <c r="E91" t="s">
         <v>134</v>
@@ -5291,10 +5291,10 @@
         <v>11</v>
       </c>
       <c r="D92" t="s">
-        <v>104</v>
+        <v>8</v>
       </c>
       <c r="E92" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F92" t="s">
         <v>133</v>
@@ -5309,7 +5309,7 @@
         <v>11</v>
       </c>
       <c r="D93" t="s">
-        <v>8</v>
+        <v>41</v>
       </c>
       <c r="E93" t="s">
         <v>135</v>
@@ -5327,7 +5327,7 @@
         <v>11</v>
       </c>
       <c r="D94" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="E94" t="s">
         <v>135</v>
@@ -5345,7 +5345,7 @@
         <v>11</v>
       </c>
       <c r="D95" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="E95" t="s">
         <v>135</v>
@@ -5363,7 +5363,7 @@
         <v>11</v>
       </c>
       <c r="D96" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="E96" t="s">
         <v>135</v>
@@ -5381,7 +5381,7 @@
         <v>11</v>
       </c>
       <c r="D97" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="E97" t="s">
         <v>135</v>
@@ -5399,7 +5399,7 @@
         <v>11</v>
       </c>
       <c r="D98" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="E98" t="s">
         <v>135</v>
@@ -5417,7 +5417,7 @@
         <v>11</v>
       </c>
       <c r="D99" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="E99" t="s">
         <v>135</v>
@@ -5435,7 +5435,7 @@
         <v>11</v>
       </c>
       <c r="D100" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="E100" t="s">
         <v>135</v>
@@ -5453,7 +5453,7 @@
         <v>11</v>
       </c>
       <c r="D101" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="E101" t="s">
         <v>135</v>
@@ -5471,7 +5471,7 @@
         <v>11</v>
       </c>
       <c r="D102" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="E102" t="s">
         <v>135</v>
@@ -5489,7 +5489,7 @@
         <v>11</v>
       </c>
       <c r="D103" t="s">
-        <v>78</v>
+        <v>92</v>
       </c>
       <c r="E103" t="s">
         <v>135</v>
@@ -5507,7 +5507,7 @@
         <v>11</v>
       </c>
       <c r="D104" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="E104" t="s">
         <v>135</v>
@@ -5525,7 +5525,7 @@
         <v>11</v>
       </c>
       <c r="D105" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="E105" t="s">
         <v>135</v>
@@ -5543,7 +5543,7 @@
         <v>11</v>
       </c>
       <c r="D106" t="s">
-        <v>87</v>
+        <v>100</v>
       </c>
       <c r="E106" t="s">
         <v>135</v>
@@ -5561,7 +5561,7 @@
         <v>11</v>
       </c>
       <c r="D107" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="E107" t="s">
         <v>135</v>
@@ -5579,7 +5579,7 @@
         <v>11</v>
       </c>
       <c r="D108" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="E108" t="s">
         <v>135</v>
@@ -5795,7 +5795,7 @@
         <v>12</v>
       </c>
       <c r="D120" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E120" t="s">
         <v>134</v>
@@ -5831,7 +5831,7 @@
         <v>12</v>
       </c>
       <c r="D122" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E122" t="s">
         <v>134</v>
@@ -5849,7 +5849,7 @@
         <v>12</v>
       </c>
       <c r="D123" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E123" t="s">
         <v>134</v>
@@ -5885,10 +5885,10 @@
         <v>12</v>
       </c>
       <c r="D125" t="s">
-        <v>8</v>
+        <v>109</v>
       </c>
       <c r="E125" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F125" t="s">
         <v>133</v>
@@ -5903,7 +5903,7 @@
         <v>12</v>
       </c>
       <c r="D126" t="s">
-        <v>41</v>
+        <v>8</v>
       </c>
       <c r="E126" t="s">
         <v>135</v>
@@ -5921,7 +5921,7 @@
         <v>12</v>
       </c>
       <c r="D127" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="E127" t="s">
         <v>135</v>
@@ -5939,7 +5939,7 @@
         <v>12</v>
       </c>
       <c r="D128" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="E128" t="s">
         <v>135</v>
@@ -5957,7 +5957,7 @@
         <v>12</v>
       </c>
       <c r="D129" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="E129" t="s">
         <v>135</v>
@@ -5975,7 +5975,7 @@
         <v>12</v>
       </c>
       <c r="D130" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="E130" t="s">
         <v>135</v>
@@ -5993,7 +5993,7 @@
         <v>12</v>
       </c>
       <c r="D131" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="E131" t="s">
         <v>135</v>
@@ -6011,7 +6011,7 @@
         <v>12</v>
       </c>
       <c r="D132" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="E132" t="s">
         <v>135</v>
@@ -6029,7 +6029,7 @@
         <v>12</v>
       </c>
       <c r="D133" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="E133" t="s">
         <v>135</v>
@@ -6047,7 +6047,7 @@
         <v>12</v>
       </c>
       <c r="D134" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="E134" t="s">
         <v>135</v>
@@ -6065,7 +6065,7 @@
         <v>12</v>
       </c>
       <c r="D135" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="E135" t="s">
         <v>135</v>
@@ -6083,7 +6083,7 @@
         <v>12</v>
       </c>
       <c r="D136" t="s">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="E136" t="s">
         <v>135</v>
@@ -6101,7 +6101,7 @@
         <v>12</v>
       </c>
       <c r="D137" t="s">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="E137" t="s">
         <v>135</v>
@@ -6119,7 +6119,7 @@
         <v>12</v>
       </c>
       <c r="D138" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="E138" t="s">
         <v>135</v>
@@ -6137,7 +6137,7 @@
         <v>12</v>
       </c>
       <c r="D139" t="s">
-        <v>99</v>
+        <v>88</v>
       </c>
       <c r="E139" t="s">
         <v>135</v>
@@ -6155,7 +6155,7 @@
         <v>12</v>
       </c>
       <c r="D140" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="E140" t="s">
         <v>135</v>
@@ -6170,13 +6170,13 @@
       </c>
       <c r="B141"/>
       <c r="C141" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D141" t="s">
-        <v>8</v>
+        <v>104</v>
       </c>
       <c r="E141" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F141" t="s">
         <v>133</v>
@@ -6188,13 +6188,13 @@
       </c>
       <c r="B142"/>
       <c r="C142" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D142" t="s">
-        <v>41</v>
+        <v>109</v>
       </c>
       <c r="E142" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F142" t="s">
         <v>133</v>
@@ -6209,7 +6209,7 @@
         <v>13</v>
       </c>
       <c r="D143" t="s">
-        <v>45</v>
+        <v>8</v>
       </c>
       <c r="E143" t="s">
         <v>134</v>
@@ -6227,7 +6227,7 @@
         <v>13</v>
       </c>
       <c r="D144" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="E144" t="s">
         <v>134</v>
@@ -6245,7 +6245,7 @@
         <v>13</v>
       </c>
       <c r="D145" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="E145" t="s">
         <v>134</v>
@@ -6263,7 +6263,7 @@
         <v>13</v>
       </c>
       <c r="D146" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="E146" t="s">
         <v>134</v>
@@ -6281,7 +6281,7 @@
         <v>13</v>
       </c>
       <c r="D147" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="E147" t="s">
         <v>134</v>
@@ -6299,7 +6299,7 @@
         <v>13</v>
       </c>
       <c r="D148" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="E148" t="s">
         <v>134</v>
@@ -6317,7 +6317,7 @@
         <v>13</v>
       </c>
       <c r="D149" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="E149" t="s">
         <v>134</v>
@@ -6335,7 +6335,7 @@
         <v>13</v>
       </c>
       <c r="D150" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="E150" t="s">
         <v>134</v>
@@ -6353,7 +6353,7 @@
         <v>13</v>
       </c>
       <c r="D151" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="E151" t="s">
         <v>134</v>
@@ -6371,7 +6371,7 @@
         <v>13</v>
       </c>
       <c r="D152" t="s">
-        <v>91</v>
+        <v>73</v>
       </c>
       <c r="E152" t="s">
         <v>134</v>
@@ -6389,7 +6389,7 @@
         <v>13</v>
       </c>
       <c r="D153" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="E153" t="s">
         <v>134</v>
@@ -6407,7 +6407,7 @@
         <v>13</v>
       </c>
       <c r="D154" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="E154" t="s">
         <v>134</v>
@@ -6425,7 +6425,7 @@
         <v>13</v>
       </c>
       <c r="D155" t="s">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="E155" t="s">
         <v>134</v>
@@ -6443,7 +6443,7 @@
         <v>13</v>
       </c>
       <c r="D156" t="s">
-        <v>99</v>
+        <v>88</v>
       </c>
       <c r="E156" t="s">
         <v>134</v>
@@ -6479,10 +6479,10 @@
         <v>13</v>
       </c>
       <c r="D158" t="s">
-        <v>8</v>
+        <v>109</v>
       </c>
       <c r="E158" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F158" t="s">
         <v>133</v>
@@ -6497,7 +6497,7 @@
         <v>13</v>
       </c>
       <c r="D159" t="s">
-        <v>41</v>
+        <v>8</v>
       </c>
       <c r="E159" t="s">
         <v>135</v>
@@ -6515,7 +6515,7 @@
         <v>13</v>
       </c>
       <c r="D160" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="E160" t="s">
         <v>135</v>
@@ -6533,7 +6533,7 @@
         <v>13</v>
       </c>
       <c r="D161" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="E161" t="s">
         <v>135</v>
@@ -6551,7 +6551,7 @@
         <v>13</v>
       </c>
       <c r="D162" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="E162" t="s">
         <v>135</v>
@@ -6569,7 +6569,7 @@
         <v>13</v>
       </c>
       <c r="D163" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="E163" t="s">
         <v>135</v>
@@ -6587,7 +6587,7 @@
         <v>13</v>
       </c>
       <c r="D164" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="E164" t="s">
         <v>135</v>
@@ -6605,7 +6605,7 @@
         <v>13</v>
       </c>
       <c r="D165" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="E165" t="s">
         <v>135</v>
@@ -6623,7 +6623,7 @@
         <v>13</v>
       </c>
       <c r="D166" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="E166" t="s">
         <v>135</v>
@@ -6641,7 +6641,7 @@
         <v>13</v>
       </c>
       <c r="D167" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="E167" t="s">
         <v>135</v>
@@ -6659,7 +6659,7 @@
         <v>13</v>
       </c>
       <c r="D168" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="E168" t="s">
         <v>135</v>
@@ -6677,7 +6677,7 @@
         <v>13</v>
       </c>
       <c r="D169" t="s">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="E169" t="s">
         <v>135</v>
@@ -6695,7 +6695,7 @@
         <v>13</v>
       </c>
       <c r="D170" t="s">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="E170" t="s">
         <v>135</v>
@@ -6713,7 +6713,7 @@
         <v>13</v>
       </c>
       <c r="D171" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="E171" t="s">
         <v>135</v>
@@ -6731,7 +6731,7 @@
         <v>13</v>
       </c>
       <c r="D172" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="E172" t="s">
         <v>135</v>
@@ -6749,7 +6749,7 @@
         <v>13</v>
       </c>
       <c r="D173" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="E173" t="s">
         <v>135</v>
@@ -6767,7 +6767,7 @@
         <v>13</v>
       </c>
       <c r="D174" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="E174" t="s">
         <v>135</v>
@@ -6983,7 +6983,7 @@
         <v>14</v>
       </c>
       <c r="D186" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E186" t="s">
         <v>134</v>
@@ -7019,7 +7019,7 @@
         <v>14</v>
       </c>
       <c r="D188" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E188" t="s">
         <v>134</v>
@@ -7037,7 +7037,7 @@
         <v>14</v>
       </c>
       <c r="D189" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="E189" t="s">
         <v>134</v>
@@ -7055,7 +7055,7 @@
         <v>14</v>
       </c>
       <c r="D190" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="E190" t="s">
         <v>134</v>
@@ -7271,7 +7271,7 @@
         <v>14</v>
       </c>
       <c r="D202" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E202" t="s">
         <v>135</v>
@@ -7307,7 +7307,7 @@
         <v>14</v>
       </c>
       <c r="D204" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E204" t="s">
         <v>135</v>
@@ -7325,7 +7325,7 @@
         <v>14</v>
       </c>
       <c r="D205" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="E205" t="s">
         <v>135</v>
@@ -7343,7 +7343,7 @@
         <v>14</v>
       </c>
       <c r="D206" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="E206" t="s">
         <v>135</v>
@@ -7559,7 +7559,7 @@
         <v>15</v>
       </c>
       <c r="D218" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E218" t="s">
         <v>134</v>
@@ -7595,7 +7595,7 @@
         <v>15</v>
       </c>
       <c r="D220" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E220" t="s">
         <v>134</v>
@@ -7613,7 +7613,7 @@
         <v>15</v>
       </c>
       <c r="D221" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="E221" t="s">
         <v>134</v>
@@ -7631,7 +7631,7 @@
         <v>15</v>
       </c>
       <c r="D222" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="E222" t="s">
         <v>134</v>
@@ -7649,7 +7649,7 @@
         <v>15</v>
       </c>
       <c r="D223" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="E223" t="s">
         <v>134</v>
@@ -7865,7 +7865,7 @@
         <v>15</v>
       </c>
       <c r="D235" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E235" t="s">
         <v>135</v>
@@ -7901,7 +7901,7 @@
         <v>15</v>
       </c>
       <c r="D237" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E237" t="s">
         <v>135</v>
@@ -7919,7 +7919,7 @@
         <v>15</v>
       </c>
       <c r="D238" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="E238" t="s">
         <v>135</v>
@@ -7937,7 +7937,7 @@
         <v>15</v>
       </c>
       <c r="D239" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="E239" t="s">
         <v>135</v>
@@ -7955,7 +7955,7 @@
         <v>15</v>
       </c>
       <c r="D240" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="E240" t="s">
         <v>135</v>
@@ -8171,7 +8171,7 @@
         <v>16</v>
       </c>
       <c r="D252" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E252" t="s">
         <v>134</v>
@@ -8207,7 +8207,7 @@
         <v>16</v>
       </c>
       <c r="D254" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E254" t="s">
         <v>134</v>
@@ -8225,7 +8225,7 @@
         <v>16</v>
       </c>
       <c r="D255" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="E255" t="s">
         <v>134</v>
@@ -8243,7 +8243,7 @@
         <v>16</v>
       </c>
       <c r="D256" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="E256" t="s">
         <v>134</v>
@@ -8459,7 +8459,7 @@
         <v>16</v>
       </c>
       <c r="D268" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E268" t="s">
         <v>135</v>
@@ -8495,7 +8495,7 @@
         <v>16</v>
       </c>
       <c r="D270" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E270" t="s">
         <v>135</v>
@@ -8513,7 +8513,7 @@
         <v>16</v>
       </c>
       <c r="D271" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="E271" t="s">
         <v>135</v>
@@ -8531,7 +8531,7 @@
         <v>16</v>
       </c>
       <c r="D272" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="E272" t="s">
         <v>135</v>
@@ -9005,7 +9005,7 @@
         <v>144</v>
       </c>
       <c r="E14" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="F14" t="n">
         <v>6.0</v>
@@ -9083,7 +9083,7 @@
         <v>144</v>
       </c>
       <c r="E16" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F16" t="n">
         <v>1.0</v>
@@ -9161,7 +9161,7 @@
         <v>144</v>
       </c>
       <c r="E18" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F18" t="n">
         <v>3.0</v>
@@ -9200,10 +9200,10 @@
         <v>144</v>
       </c>
       <c r="E19" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F19" t="n">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="G19"/>
       <c r="H19" t="s">
@@ -9224,7 +9224,7 @@
       <c r="M19"/>
       <c r="N19"/>
       <c r="O19" t="s">
-        <v>205</v>
+        <v>39</v>
       </c>
     </row>
     <row r="20">
@@ -9236,13 +9236,13 @@
         <v>7</v>
       </c>
       <c r="D20" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="E20" t="s">
-        <v>8</v>
+        <v>100</v>
       </c>
       <c r="F20" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
       <c r="G20"/>
       <c r="H20" t="s">
@@ -9252,13 +9252,13 @@
         <v>230</v>
       </c>
       <c r="J20" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="K20" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="L20" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="M20"/>
       <c r="N20"/>
@@ -9278,10 +9278,10 @@
         <v>148</v>
       </c>
       <c r="E21" t="s">
-        <v>41</v>
+        <v>8</v>
       </c>
       <c r="F21" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G21"/>
       <c r="H21" t="s">
@@ -9317,10 +9317,10 @@
         <v>148</v>
       </c>
       <c r="E22" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="F22" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="G22"/>
       <c r="H22" t="s">
@@ -9356,10 +9356,10 @@
         <v>148</v>
       </c>
       <c r="E23" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="F23" t="n">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
       <c r="G23"/>
       <c r="H23" t="s">
@@ -9395,10 +9395,10 @@
         <v>148</v>
       </c>
       <c r="E24" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="F24" t="n">
-        <v>5.0</v>
+        <v>4.0</v>
       </c>
       <c r="G24"/>
       <c r="H24" t="s">
@@ -9434,10 +9434,10 @@
         <v>148</v>
       </c>
       <c r="E25" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="F25" t="n">
-        <v>1.0</v>
+        <v>5.0</v>
       </c>
       <c r="G25"/>
       <c r="H25" t="s">
@@ -9447,13 +9447,13 @@
         <v>230</v>
       </c>
       <c r="J25" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="K25" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="L25" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="M25"/>
       <c r="N25"/>
@@ -9473,10 +9473,10 @@
         <v>148</v>
       </c>
       <c r="E26" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="F26" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G26"/>
       <c r="H26" t="s">
@@ -9512,10 +9512,10 @@
         <v>148</v>
       </c>
       <c r="E27" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="F27" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="G27"/>
       <c r="H27" t="s">
@@ -9551,10 +9551,10 @@
         <v>148</v>
       </c>
       <c r="E28" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="F28" t="n">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
       <c r="G28"/>
       <c r="H28" t="s">
@@ -9590,10 +9590,10 @@
         <v>148</v>
       </c>
       <c r="E29" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="F29" t="n">
-        <v>5.0</v>
+        <v>4.0</v>
       </c>
       <c r="G29"/>
       <c r="H29" t="s">
@@ -9629,10 +9629,10 @@
         <v>148</v>
       </c>
       <c r="E30" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="F30" t="n">
-        <v>6.0</v>
+        <v>5.0</v>
       </c>
       <c r="G30"/>
       <c r="H30" t="s">
@@ -9668,10 +9668,10 @@
         <v>148</v>
       </c>
       <c r="E31" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="F31" t="n">
-        <v>1.0</v>
+        <v>6.0</v>
       </c>
       <c r="G31"/>
       <c r="H31" t="s">
@@ -9681,18 +9681,18 @@
         <v>230</v>
       </c>
       <c r="J31" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="K31" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="L31" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="M31"/>
       <c r="N31"/>
       <c r="O31" t="s">
-        <v>39</v>
+        <v>205</v>
       </c>
     </row>
     <row r="32">
@@ -9707,10 +9707,10 @@
         <v>148</v>
       </c>
       <c r="E32" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="F32" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G32"/>
       <c r="H32" t="s">
@@ -9746,10 +9746,10 @@
         <v>148</v>
       </c>
       <c r="E33" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="F33" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="G33"/>
       <c r="H33" t="s">
@@ -9785,10 +9785,10 @@
         <v>148</v>
       </c>
       <c r="E34" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="F34" t="n">
-        <v>4.0</v>
+        <v>6.0</v>
       </c>
       <c r="G34"/>
       <c r="H34" t="s">
@@ -9809,7 +9809,7 @@
       <c r="M34"/>
       <c r="N34"/>
       <c r="O34" t="s">
-        <v>205</v>
+        <v>39</v>
       </c>
     </row>
     <row r="35">
@@ -9821,29 +9821,29 @@
         <v>7</v>
       </c>
       <c r="D35" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E35" t="s">
-        <v>8</v>
+        <v>92</v>
       </c>
       <c r="F35" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="G35"/>
       <c r="H35" t="s">
-        <v>205</v>
+        <v>39</v>
       </c>
       <c r="I35" t="s">
         <v>230</v>
       </c>
       <c r="J35" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="K35" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="L35" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="M35"/>
       <c r="N35"/>
@@ -9860,34 +9860,34 @@
         <v>7</v>
       </c>
       <c r="D36" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E36" t="s">
-        <v>41</v>
+        <v>100</v>
       </c>
       <c r="F36" t="n">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
       <c r="G36"/>
       <c r="H36" t="s">
-        <v>205</v>
+        <v>39</v>
       </c>
       <c r="I36" t="s">
         <v>230</v>
       </c>
       <c r="J36" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="K36" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="L36" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="M36"/>
       <c r="N36"/>
       <c r="O36" t="s">
-        <v>39</v>
+        <v>205</v>
       </c>
     </row>
     <row r="37">
@@ -9902,10 +9902,10 @@
         <v>149</v>
       </c>
       <c r="E37" t="s">
-        <v>45</v>
+        <v>8</v>
       </c>
       <c r="F37" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="G37"/>
       <c r="H37" t="s">
@@ -9941,10 +9941,10 @@
         <v>149</v>
       </c>
       <c r="E38" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="F38" t="n">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
       <c r="G38"/>
       <c r="H38" t="s">
@@ -9980,10 +9980,10 @@
         <v>149</v>
       </c>
       <c r="E39" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="F39" t="n">
-        <v>5.0</v>
+        <v>3.0</v>
       </c>
       <c r="G39"/>
       <c r="H39" t="s">
@@ -10019,10 +10019,10 @@
         <v>149</v>
       </c>
       <c r="E40" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="F40" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
       <c r="G40"/>
       <c r="H40" t="s">
@@ -10032,13 +10032,13 @@
         <v>230</v>
       </c>
       <c r="J40" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="K40" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="L40" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="M40"/>
       <c r="N40"/>
@@ -10058,10 +10058,10 @@
         <v>149</v>
       </c>
       <c r="E41" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="F41" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
       <c r="G41"/>
       <c r="H41" t="s">
@@ -10071,13 +10071,13 @@
         <v>230</v>
       </c>
       <c r="J41" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="K41" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="L41" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="M41"/>
       <c r="N41"/>
@@ -10097,10 +10097,10 @@
         <v>149</v>
       </c>
       <c r="E42" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="F42" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="G42"/>
       <c r="H42" t="s">
@@ -10136,10 +10136,10 @@
         <v>149</v>
       </c>
       <c r="E43" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="F43" t="n">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
       <c r="G43"/>
       <c r="H43" t="s">
@@ -10175,10 +10175,10 @@
         <v>149</v>
       </c>
       <c r="E44" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="F44" t="n">
-        <v>5.0</v>
+        <v>3.0</v>
       </c>
       <c r="G44"/>
       <c r="H44" t="s">
@@ -10214,10 +10214,10 @@
         <v>149</v>
       </c>
       <c r="E45" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="F45" t="n">
-        <v>6.0</v>
+        <v>4.0</v>
       </c>
       <c r="G45"/>
       <c r="H45" t="s">
@@ -10253,10 +10253,10 @@
         <v>149</v>
       </c>
       <c r="E46" t="s">
-        <v>87</v>
+        <v>73</v>
       </c>
       <c r="F46" t="n">
-        <v>1.0</v>
+        <v>5.0</v>
       </c>
       <c r="G46"/>
       <c r="H46" t="s">
@@ -10266,13 +10266,13 @@
         <v>230</v>
       </c>
       <c r="J46" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="K46" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="L46" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="M46"/>
       <c r="N46"/>
@@ -10292,10 +10292,10 @@
         <v>149</v>
       </c>
       <c r="E47" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="F47" t="n">
-        <v>2.0</v>
+        <v>6.0</v>
       </c>
       <c r="G47"/>
       <c r="H47" t="s">
@@ -10305,13 +10305,13 @@
         <v>230</v>
       </c>
       <c r="J47" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="K47" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="L47" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="M47"/>
       <c r="N47"/>
@@ -10331,10 +10331,10 @@
         <v>149</v>
       </c>
       <c r="E48" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="F48" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="G48"/>
       <c r="H48" t="s">
@@ -10364,37 +10364,37 @@
       </c>
       <c r="B49"/>
       <c r="C49" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D49" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="E49" t="s">
-        <v>8</v>
+        <v>83</v>
       </c>
       <c r="F49" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G49"/>
       <c r="H49" t="s">
-        <v>39</v>
+        <v>205</v>
       </c>
       <c r="I49" t="s">
         <v>230</v>
       </c>
       <c r="J49" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="K49" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="L49" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="M49"/>
       <c r="N49"/>
       <c r="O49" t="s">
-        <v>205</v>
+        <v>39</v>
       </c>
     </row>
     <row r="50">
@@ -10403,37 +10403,37 @@
       </c>
       <c r="B50"/>
       <c r="C50" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D50" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="E50" t="s">
-        <v>41</v>
+        <v>92</v>
       </c>
       <c r="F50" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="G50"/>
       <c r="H50" t="s">
-        <v>39</v>
+        <v>205</v>
       </c>
       <c r="I50" t="s">
         <v>230</v>
       </c>
       <c r="J50" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="K50" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="L50" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="M50"/>
       <c r="N50"/>
       <c r="O50" t="s">
-        <v>205</v>
+        <v>39</v>
       </c>
     </row>
     <row r="51">
@@ -10448,10 +10448,10 @@
         <v>144</v>
       </c>
       <c r="E51" t="s">
-        <v>45</v>
+        <v>8</v>
       </c>
       <c r="F51" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="G51"/>
       <c r="H51" t="s">
@@ -10487,10 +10487,10 @@
         <v>144</v>
       </c>
       <c r="E52" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="F52" t="n">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
       <c r="G52"/>
       <c r="H52" t="s">
@@ -10526,10 +10526,10 @@
         <v>144</v>
       </c>
       <c r="E53" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="F53" t="n">
-        <v>5.0</v>
+        <v>3.0</v>
       </c>
       <c r="G53"/>
       <c r="H53" t="s">
@@ -10565,10 +10565,10 @@
         <v>144</v>
       </c>
       <c r="E54" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="F54" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
       <c r="G54"/>
       <c r="H54" t="s">
@@ -10578,13 +10578,13 @@
         <v>230</v>
       </c>
       <c r="J54" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="K54" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="L54" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="M54"/>
       <c r="N54"/>
@@ -10604,10 +10604,10 @@
         <v>144</v>
       </c>
       <c r="E55" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="F55" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
       <c r="G55"/>
       <c r="H55" t="s">
@@ -10617,13 +10617,13 @@
         <v>230</v>
       </c>
       <c r="J55" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="K55" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="L55" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="M55"/>
       <c r="N55"/>
@@ -10643,10 +10643,10 @@
         <v>144</v>
       </c>
       <c r="E56" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="F56" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="G56"/>
       <c r="H56" t="s">
@@ -10682,10 +10682,10 @@
         <v>144</v>
       </c>
       <c r="E57" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="F57" t="n">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
       <c r="G57"/>
       <c r="H57" t="s">
@@ -10721,10 +10721,10 @@
         <v>144</v>
       </c>
       <c r="E58" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="F58" t="n">
-        <v>5.0</v>
+        <v>3.0</v>
       </c>
       <c r="G58"/>
       <c r="H58" t="s">
@@ -10760,10 +10760,10 @@
         <v>144</v>
       </c>
       <c r="E59" t="s">
-        <v>99</v>
+        <v>69</v>
       </c>
       <c r="F59" t="n">
-        <v>6.0</v>
+        <v>4.0</v>
       </c>
       <c r="G59"/>
       <c r="H59" t="s">
@@ -10799,10 +10799,10 @@
         <v>144</v>
       </c>
       <c r="E60" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="F60" t="n">
-        <v>7.0</v>
+        <v>5.0</v>
       </c>
       <c r="G60"/>
       <c r="H60" t="s">
@@ -10838,10 +10838,10 @@
         <v>144</v>
       </c>
       <c r="E61" t="s">
-        <v>87</v>
+        <v>104</v>
       </c>
       <c r="F61" t="n">
-        <v>1.0</v>
+        <v>6.0</v>
       </c>
       <c r="G61"/>
       <c r="H61" t="s">
@@ -10851,18 +10851,18 @@
         <v>230</v>
       </c>
       <c r="J61" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="K61" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="L61" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="M61"/>
       <c r="N61"/>
       <c r="O61" t="s">
-        <v>39</v>
+        <v>205</v>
       </c>
     </row>
     <row r="62">
@@ -10877,10 +10877,10 @@
         <v>144</v>
       </c>
       <c r="E62" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="F62" t="n">
-        <v>2.0</v>
+        <v>7.0</v>
       </c>
       <c r="G62"/>
       <c r="H62" t="s">
@@ -10890,18 +10890,18 @@
         <v>230</v>
       </c>
       <c r="J62" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="K62" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="L62" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="M62"/>
       <c r="N62"/>
       <c r="O62" t="s">
-        <v>39</v>
+        <v>205</v>
       </c>
     </row>
     <row r="63">
@@ -10916,10 +10916,10 @@
         <v>144</v>
       </c>
       <c r="E63" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="F63" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="G63"/>
       <c r="H63" t="s">
@@ -10955,10 +10955,10 @@
         <v>144</v>
       </c>
       <c r="E64" t="s">
-        <v>109</v>
+        <v>83</v>
       </c>
       <c r="F64" t="n">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
       <c r="G64"/>
       <c r="H64" t="s">
@@ -10994,10 +10994,10 @@
         <v>144</v>
       </c>
       <c r="E65" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="F65" t="n">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
       <c r="G65"/>
       <c r="H65" t="s">
@@ -11018,7 +11018,7 @@
       <c r="M65"/>
       <c r="N65"/>
       <c r="O65" t="s">
-        <v>205</v>
+        <v>39</v>
       </c>
     </row>
     <row r="66">
@@ -11462,7 +11462,7 @@
         <v>148</v>
       </c>
       <c r="E77" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F77" t="n">
         <v>1.0</v>
@@ -11540,10 +11540,10 @@
         <v>148</v>
       </c>
       <c r="E79" t="s">
-        <v>108</v>
+        <v>92</v>
       </c>
       <c r="F79" t="n">
-        <v>6.0</v>
+        <v>3.0</v>
       </c>
       <c r="G79"/>
       <c r="H79" t="s">
@@ -11576,29 +11576,29 @@
         <v>10</v>
       </c>
       <c r="D80" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E80" t="s">
-        <v>91</v>
+        <v>8</v>
       </c>
       <c r="F80" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="G80"/>
       <c r="H80" t="s">
-        <v>39</v>
+        <v>205</v>
       </c>
       <c r="I80" t="s">
         <v>230</v>
       </c>
       <c r="J80" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="K80" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="L80" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="M80"/>
       <c r="N80"/>
@@ -11615,34 +11615,34 @@
         <v>10</v>
       </c>
       <c r="D81" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E81" t="s">
-        <v>95</v>
+        <v>41</v>
       </c>
       <c r="F81" t="n">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
       <c r="G81"/>
       <c r="H81" t="s">
-        <v>39</v>
+        <v>205</v>
       </c>
       <c r="I81" t="s">
         <v>230</v>
       </c>
       <c r="J81" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="K81" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="L81" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="M81"/>
       <c r="N81"/>
       <c r="O81" t="s">
-        <v>205</v>
+        <v>39</v>
       </c>
     </row>
     <row r="82">
@@ -11657,10 +11657,10 @@
         <v>149</v>
       </c>
       <c r="E82" t="s">
-        <v>8</v>
+        <v>45</v>
       </c>
       <c r="F82" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="G82"/>
       <c r="H82" t="s">
@@ -11696,10 +11696,10 @@
         <v>149</v>
       </c>
       <c r="E83" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="F83" t="n">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
       <c r="G83"/>
       <c r="H83" t="s">
@@ -11735,10 +11735,10 @@
         <v>149</v>
       </c>
       <c r="E84" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="F84" t="n">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
       <c r="G84"/>
       <c r="H84" t="s">
@@ -11774,10 +11774,10 @@
         <v>149</v>
       </c>
       <c r="E85" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="F85" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
       <c r="G85"/>
       <c r="H85" t="s">
@@ -11787,13 +11787,13 @@
         <v>230</v>
       </c>
       <c r="J85" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="K85" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="L85" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="M85"/>
       <c r="N85"/>
@@ -11813,10 +11813,10 @@
         <v>149</v>
       </c>
       <c r="E86" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="F86" t="n">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
       <c r="G86"/>
       <c r="H86" t="s">
@@ -11826,13 +11826,13 @@
         <v>230</v>
       </c>
       <c r="J86" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="K86" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="L86" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="M86"/>
       <c r="N86"/>
@@ -11852,10 +11852,10 @@
         <v>149</v>
       </c>
       <c r="E87" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="F87" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="G87"/>
       <c r="H87" t="s">
@@ -11891,10 +11891,10 @@
         <v>149</v>
       </c>
       <c r="E88" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="F88" t="n">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
       <c r="G88"/>
       <c r="H88" t="s">
@@ -11930,10 +11930,10 @@
         <v>149</v>
       </c>
       <c r="E89" t="s">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="F89" t="n">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
       <c r="G89"/>
       <c r="H89" t="s">
@@ -11969,10 +11969,10 @@
         <v>149</v>
       </c>
       <c r="E90" t="s">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="F90" t="n">
-        <v>4.0</v>
+        <v>6.0</v>
       </c>
       <c r="G90"/>
       <c r="H90" t="s">
@@ -12008,10 +12008,10 @@
         <v>149</v>
       </c>
       <c r="E91" t="s">
-        <v>73</v>
+        <v>88</v>
       </c>
       <c r="F91" t="n">
-        <v>5.0</v>
+        <v>1.0</v>
       </c>
       <c r="G91"/>
       <c r="H91" t="s">
@@ -12021,13 +12021,13 @@
         <v>230</v>
       </c>
       <c r="J91" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="K91" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="L91" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="M91"/>
       <c r="N91"/>
@@ -12047,10 +12047,10 @@
         <v>149</v>
       </c>
       <c r="E92" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="F92" t="n">
-        <v>6.0</v>
+        <v>2.0</v>
       </c>
       <c r="G92"/>
       <c r="H92" t="s">
@@ -12060,13 +12060,13 @@
         <v>230</v>
       </c>
       <c r="J92" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="K92" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="L92" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="M92"/>
       <c r="N92"/>
@@ -12086,10 +12086,10 @@
         <v>149</v>
       </c>
       <c r="E93" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="F93" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="G93"/>
       <c r="H93" t="s">
@@ -12119,37 +12119,37 @@
       </c>
       <c r="B94"/>
       <c r="C94" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D94" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="E94" t="s">
-        <v>83</v>
+        <v>8</v>
       </c>
       <c r="F94" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G94"/>
       <c r="H94" t="s">
-        <v>205</v>
+        <v>39</v>
       </c>
       <c r="I94" t="s">
         <v>230</v>
       </c>
       <c r="J94" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="K94" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="L94" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="M94"/>
       <c r="N94"/>
       <c r="O94" t="s">
-        <v>39</v>
+        <v>205</v>
       </c>
     </row>
     <row r="95">
@@ -12158,37 +12158,37 @@
       </c>
       <c r="B95"/>
       <c r="C95" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D95" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="E95" t="s">
-        <v>91</v>
+        <v>41</v>
       </c>
       <c r="F95" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="G95"/>
       <c r="H95" t="s">
-        <v>205</v>
+        <v>39</v>
       </c>
       <c r="I95" t="s">
         <v>230</v>
       </c>
       <c r="J95" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="K95" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="L95" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="M95"/>
       <c r="N95"/>
       <c r="O95" t="s">
-        <v>39</v>
+        <v>205</v>
       </c>
     </row>
     <row r="96">
@@ -12203,10 +12203,10 @@
         <v>144</v>
       </c>
       <c r="E96" t="s">
-        <v>8</v>
+        <v>45</v>
       </c>
       <c r="F96" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="G96"/>
       <c r="H96" t="s">
@@ -12242,10 +12242,10 @@
         <v>144</v>
       </c>
       <c r="E97" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="F97" t="n">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
       <c r="G97"/>
       <c r="H97" t="s">
@@ -12281,10 +12281,10 @@
         <v>144</v>
       </c>
       <c r="E98" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="F98" t="n">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
       <c r="G98"/>
       <c r="H98" t="s">
@@ -12320,10 +12320,10 @@
         <v>144</v>
       </c>
       <c r="E99" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="F99" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
       <c r="G99"/>
       <c r="H99" t="s">
@@ -12333,13 +12333,13 @@
         <v>230</v>
       </c>
       <c r="J99" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="K99" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="L99" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="M99"/>
       <c r="N99"/>
@@ -12359,10 +12359,10 @@
         <v>144</v>
       </c>
       <c r="E100" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="F100" t="n">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
       <c r="G100"/>
       <c r="H100" t="s">
@@ -12372,13 +12372,13 @@
         <v>230</v>
       </c>
       <c r="J100" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="K100" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="L100" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="M100"/>
       <c r="N100"/>
@@ -12398,10 +12398,10 @@
         <v>144</v>
       </c>
       <c r="E101" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="F101" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="G101"/>
       <c r="H101" t="s">
@@ -12437,10 +12437,10 @@
         <v>144</v>
       </c>
       <c r="E102" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="F102" t="n">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
       <c r="G102"/>
       <c r="H102" t="s">
@@ -12476,10 +12476,10 @@
         <v>144</v>
       </c>
       <c r="E103" t="s">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="F103" t="n">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
       <c r="G103"/>
       <c r="H103" t="s">
@@ -12515,10 +12515,10 @@
         <v>144</v>
       </c>
       <c r="E104" t="s">
-        <v>69</v>
+        <v>104</v>
       </c>
       <c r="F104" t="n">
-        <v>4.0</v>
+        <v>6.0</v>
       </c>
       <c r="G104"/>
       <c r="H104" t="s">
@@ -12554,10 +12554,10 @@
         <v>144</v>
       </c>
       <c r="E105" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="F105" t="n">
-        <v>5.0</v>
+        <v>7.0</v>
       </c>
       <c r="G105"/>
       <c r="H105" t="s">
@@ -12593,10 +12593,10 @@
         <v>144</v>
       </c>
       <c r="E106" t="s">
-        <v>99</v>
+        <v>88</v>
       </c>
       <c r="F106" t="n">
-        <v>6.0</v>
+        <v>1.0</v>
       </c>
       <c r="G106"/>
       <c r="H106" t="s">
@@ -12606,18 +12606,18 @@
         <v>230</v>
       </c>
       <c r="J106" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="K106" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="L106" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="M106"/>
       <c r="N106"/>
       <c r="O106" t="s">
-        <v>205</v>
+        <v>39</v>
       </c>
     </row>
     <row r="107">
@@ -12632,10 +12632,10 @@
         <v>144</v>
       </c>
       <c r="E107" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="F107" t="n">
-        <v>7.0</v>
+        <v>2.0</v>
       </c>
       <c r="G107"/>
       <c r="H107" t="s">
@@ -12645,18 +12645,18 @@
         <v>230</v>
       </c>
       <c r="J107" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="K107" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="L107" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="M107"/>
       <c r="N107"/>
       <c r="O107" t="s">
-        <v>205</v>
+        <v>39</v>
       </c>
     </row>
     <row r="108">
@@ -12671,10 +12671,10 @@
         <v>144</v>
       </c>
       <c r="E108" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="F108" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="G108"/>
       <c r="H108" t="s">
@@ -12710,10 +12710,10 @@
         <v>144</v>
       </c>
       <c r="E109" t="s">
-        <v>83</v>
+        <v>100</v>
       </c>
       <c r="F109" t="n">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
       <c r="G109"/>
       <c r="H109" t="s">
@@ -12734,7 +12734,7 @@
       <c r="M109"/>
       <c r="N109"/>
       <c r="O109" t="s">
-        <v>39</v>
+        <v>205</v>
       </c>
     </row>
     <row r="110">
@@ -12746,13 +12746,13 @@
         <v>11</v>
       </c>
       <c r="D110" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="E110" t="s">
-        <v>91</v>
+        <v>8</v>
       </c>
       <c r="F110" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="G110"/>
       <c r="H110" t="s">
@@ -12762,18 +12762,18 @@
         <v>230</v>
       </c>
       <c r="J110" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="K110" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="L110" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="M110"/>
       <c r="N110"/>
       <c r="O110" t="s">
-        <v>39</v>
+        <v>205</v>
       </c>
     </row>
     <row r="111">
@@ -12788,10 +12788,10 @@
         <v>148</v>
       </c>
       <c r="E111" t="s">
-        <v>8</v>
+        <v>41</v>
       </c>
       <c r="F111" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G111"/>
       <c r="H111" t="s">
@@ -12827,10 +12827,10 @@
         <v>148</v>
       </c>
       <c r="E112" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="F112" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="G112"/>
       <c r="H112" t="s">
@@ -12866,10 +12866,10 @@
         <v>148</v>
       </c>
       <c r="E113" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="F113" t="n">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="G113"/>
       <c r="H113" t="s">
@@ -12905,10 +12905,10 @@
         <v>148</v>
       </c>
       <c r="E114" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="F114" t="n">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="G114"/>
       <c r="H114" t="s">
@@ -12944,10 +12944,10 @@
         <v>148</v>
       </c>
       <c r="E115" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="F115" t="n">
-        <v>5.0</v>
+        <v>1.0</v>
       </c>
       <c r="G115"/>
       <c r="H115" t="s">
@@ -12957,13 +12957,13 @@
         <v>230</v>
       </c>
       <c r="J115" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="K115" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="L115" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="M115"/>
       <c r="N115"/>
@@ -12983,10 +12983,10 @@
         <v>148</v>
       </c>
       <c r="E116" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="F116" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G116"/>
       <c r="H116" t="s">
@@ -13022,10 +13022,10 @@
         <v>148</v>
       </c>
       <c r="E117" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="F117" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="G117"/>
       <c r="H117" t="s">
@@ -13061,10 +13061,10 @@
         <v>148</v>
       </c>
       <c r="E118" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="F118" t="n">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="G118"/>
       <c r="H118" t="s">
@@ -13100,10 +13100,10 @@
         <v>148</v>
       </c>
       <c r="E119" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="F119" t="n">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="G119"/>
       <c r="H119" t="s">
@@ -13139,10 +13139,10 @@
         <v>148</v>
       </c>
       <c r="E120" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="F120" t="n">
-        <v>5.0</v>
+        <v>6.0</v>
       </c>
       <c r="G120"/>
       <c r="H120" t="s">
@@ -13178,10 +13178,10 @@
         <v>148</v>
       </c>
       <c r="E121" t="s">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="F121" t="n">
-        <v>6.0</v>
+        <v>1.0</v>
       </c>
       <c r="G121"/>
       <c r="H121" t="s">
@@ -13191,18 +13191,18 @@
         <v>230</v>
       </c>
       <c r="J121" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="K121" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="L121" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="M121"/>
       <c r="N121"/>
       <c r="O121" t="s">
-        <v>205</v>
+        <v>39</v>
       </c>
     </row>
     <row r="122">
@@ -13217,10 +13217,10 @@
         <v>148</v>
       </c>
       <c r="E122" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="F122" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G122"/>
       <c r="H122" t="s">
@@ -13256,10 +13256,10 @@
         <v>148</v>
       </c>
       <c r="E123" t="s">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="F123" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="G123"/>
       <c r="H123" t="s">
@@ -13295,10 +13295,10 @@
         <v>148</v>
       </c>
       <c r="E124" t="s">
-        <v>91</v>
+        <v>100</v>
       </c>
       <c r="F124" t="n">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="G124"/>
       <c r="H124" t="s">
@@ -13319,7 +13319,7 @@
       <c r="M124"/>
       <c r="N124"/>
       <c r="O124" t="s">
-        <v>39</v>
+        <v>205</v>
       </c>
     </row>
     <row r="125">
@@ -13763,7 +13763,7 @@
         <v>149</v>
       </c>
       <c r="E136" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F136" t="n">
         <v>1.0</v>
@@ -13841,7 +13841,7 @@
         <v>149</v>
       </c>
       <c r="E138" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F138" t="n">
         <v>3.0</v>
@@ -14270,7 +14270,7 @@
         <v>144</v>
       </c>
       <c r="E149" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="F149" t="n">
         <v>6.0</v>
@@ -14348,7 +14348,7 @@
         <v>144</v>
       </c>
       <c r="E151" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F151" t="n">
         <v>1.0</v>
@@ -14426,7 +14426,7 @@
         <v>144</v>
       </c>
       <c r="E153" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F153" t="n">
         <v>3.0</v>
@@ -14462,13 +14462,13 @@
         <v>12</v>
       </c>
       <c r="D154" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="E154" t="s">
-        <v>8</v>
+        <v>100</v>
       </c>
       <c r="F154" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
       <c r="G154"/>
       <c r="H154" t="s">
@@ -14478,13 +14478,13 @@
         <v>230</v>
       </c>
       <c r="J154" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="K154" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="L154" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="M154"/>
       <c r="N154"/>
@@ -14504,10 +14504,10 @@
         <v>148</v>
       </c>
       <c r="E155" t="s">
-        <v>41</v>
+        <v>8</v>
       </c>
       <c r="F155" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G155"/>
       <c r="H155" t="s">
@@ -14543,10 +14543,10 @@
         <v>148</v>
       </c>
       <c r="E156" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="F156" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="G156"/>
       <c r="H156" t="s">
@@ -14582,10 +14582,10 @@
         <v>148</v>
       </c>
       <c r="E157" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="F157" t="n">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
       <c r="G157"/>
       <c r="H157" t="s">
@@ -14621,10 +14621,10 @@
         <v>148</v>
       </c>
       <c r="E158" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="F158" t="n">
-        <v>5.0</v>
+        <v>4.0</v>
       </c>
       <c r="G158"/>
       <c r="H158" t="s">
@@ -14660,10 +14660,10 @@
         <v>148</v>
       </c>
       <c r="E159" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="F159" t="n">
-        <v>1.0</v>
+        <v>5.0</v>
       </c>
       <c r="G159"/>
       <c r="H159" t="s">
@@ -14673,13 +14673,13 @@
         <v>230</v>
       </c>
       <c r="J159" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="K159" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="L159" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="M159"/>
       <c r="N159"/>
@@ -14699,10 +14699,10 @@
         <v>148</v>
       </c>
       <c r="E160" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="F160" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G160"/>
       <c r="H160" t="s">
@@ -14738,10 +14738,10 @@
         <v>148</v>
       </c>
       <c r="E161" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="F161" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="G161"/>
       <c r="H161" t="s">
@@ -14777,10 +14777,10 @@
         <v>148</v>
       </c>
       <c r="E162" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="F162" t="n">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
       <c r="G162"/>
       <c r="H162" t="s">
@@ -14816,10 +14816,10 @@
         <v>148</v>
       </c>
       <c r="E163" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="F163" t="n">
-        <v>5.0</v>
+        <v>4.0</v>
       </c>
       <c r="G163"/>
       <c r="H163" t="s">
@@ -14855,10 +14855,10 @@
         <v>148</v>
       </c>
       <c r="E164" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="F164" t="n">
-        <v>6.0</v>
+        <v>5.0</v>
       </c>
       <c r="G164"/>
       <c r="H164" t="s">
@@ -14894,10 +14894,10 @@
         <v>148</v>
       </c>
       <c r="E165" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="F165" t="n">
-        <v>1.0</v>
+        <v>6.0</v>
       </c>
       <c r="G165"/>
       <c r="H165" t="s">
@@ -14907,18 +14907,18 @@
         <v>230</v>
       </c>
       <c r="J165" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="K165" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="L165" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="M165"/>
       <c r="N165"/>
       <c r="O165" t="s">
-        <v>39</v>
+        <v>205</v>
       </c>
     </row>
     <row r="166">
@@ -14933,10 +14933,10 @@
         <v>148</v>
       </c>
       <c r="E166" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="F166" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G166"/>
       <c r="H166" t="s">
@@ -14972,10 +14972,10 @@
         <v>148</v>
       </c>
       <c r="E167" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="F167" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="G167"/>
       <c r="H167" t="s">
@@ -15008,29 +15008,29 @@
         <v>12</v>
       </c>
       <c r="D168" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E168" t="s">
-        <v>8</v>
+        <v>92</v>
       </c>
       <c r="F168" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="G168"/>
       <c r="H168" t="s">
-        <v>205</v>
+        <v>39</v>
       </c>
       <c r="I168" t="s">
         <v>230</v>
       </c>
       <c r="J168" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="K168" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="L168" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="M168"/>
       <c r="N168"/>
@@ -15047,34 +15047,34 @@
         <v>12</v>
       </c>
       <c r="D169" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E169" t="s">
-        <v>41</v>
+        <v>100</v>
       </c>
       <c r="F169" t="n">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
       <c r="G169"/>
       <c r="H169" t="s">
-        <v>205</v>
+        <v>39</v>
       </c>
       <c r="I169" t="s">
         <v>230</v>
       </c>
       <c r="J169" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="K169" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="L169" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="M169"/>
       <c r="N169"/>
       <c r="O169" t="s">
-        <v>39</v>
+        <v>205</v>
       </c>
     </row>
     <row r="170">
@@ -15089,10 +15089,10 @@
         <v>149</v>
       </c>
       <c r="E170" t="s">
-        <v>45</v>
+        <v>8</v>
       </c>
       <c r="F170" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="G170"/>
       <c r="H170" t="s">
@@ -15128,10 +15128,10 @@
         <v>149</v>
       </c>
       <c r="E171" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="F171" t="n">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
       <c r="G171"/>
       <c r="H171" t="s">
@@ -15167,10 +15167,10 @@
         <v>149</v>
       </c>
       <c r="E172" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="F172" t="n">
-        <v>5.0</v>
+        <v>3.0</v>
       </c>
       <c r="G172"/>
       <c r="H172" t="s">
@@ -15206,10 +15206,10 @@
         <v>149</v>
       </c>
       <c r="E173" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="F173" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
       <c r="G173"/>
       <c r="H173" t="s">
@@ -15219,13 +15219,13 @@
         <v>230</v>
       </c>
       <c r="J173" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="K173" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="L173" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="M173"/>
       <c r="N173"/>
@@ -15245,10 +15245,10 @@
         <v>149</v>
       </c>
       <c r="E174" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="F174" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
       <c r="G174"/>
       <c r="H174" t="s">
@@ -15258,13 +15258,13 @@
         <v>230</v>
       </c>
       <c r="J174" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="K174" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="L174" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="M174"/>
       <c r="N174"/>
@@ -15284,10 +15284,10 @@
         <v>149</v>
       </c>
       <c r="E175" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="F175" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="G175"/>
       <c r="H175" t="s">
@@ -15323,10 +15323,10 @@
         <v>149</v>
       </c>
       <c r="E176" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="F176" t="n">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
       <c r="G176"/>
       <c r="H176" t="s">
@@ -15362,10 +15362,10 @@
         <v>149</v>
       </c>
       <c r="E177" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="F177" t="n">
-        <v>5.0</v>
+        <v>3.0</v>
       </c>
       <c r="G177"/>
       <c r="H177" t="s">
@@ -15401,10 +15401,10 @@
         <v>149</v>
       </c>
       <c r="E178" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="F178" t="n">
-        <v>6.0</v>
+        <v>4.0</v>
       </c>
       <c r="G178"/>
       <c r="H178" t="s">
@@ -15440,10 +15440,10 @@
         <v>149</v>
       </c>
       <c r="E179" t="s">
-        <v>87</v>
+        <v>73</v>
       </c>
       <c r="F179" t="n">
-        <v>1.0</v>
+        <v>5.0</v>
       </c>
       <c r="G179"/>
       <c r="H179" t="s">
@@ -15453,13 +15453,13 @@
         <v>230</v>
       </c>
       <c r="J179" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="K179" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="L179" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="M179"/>
       <c r="N179"/>
@@ -15479,10 +15479,10 @@
         <v>149</v>
       </c>
       <c r="E180" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="F180" t="n">
-        <v>2.0</v>
+        <v>6.0</v>
       </c>
       <c r="G180"/>
       <c r="H180" t="s">
@@ -15492,13 +15492,13 @@
         <v>230</v>
       </c>
       <c r="J180" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="K180" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="L180" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="M180"/>
       <c r="N180"/>
@@ -15518,10 +15518,10 @@
         <v>149</v>
       </c>
       <c r="E181" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="F181" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="G181"/>
       <c r="H181" t="s">
@@ -15551,37 +15551,37 @@
       </c>
       <c r="B182"/>
       <c r="C182" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D182" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="E182" t="s">
-        <v>8</v>
+        <v>83</v>
       </c>
       <c r="F182" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G182"/>
       <c r="H182" t="s">
-        <v>39</v>
+        <v>205</v>
       </c>
       <c r="I182" t="s">
         <v>230</v>
       </c>
       <c r="J182" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="K182" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="L182" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="M182"/>
       <c r="N182"/>
       <c r="O182" t="s">
-        <v>205</v>
+        <v>39</v>
       </c>
     </row>
     <row r="183">
@@ -15590,37 +15590,37 @@
       </c>
       <c r="B183"/>
       <c r="C183" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D183" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="E183" t="s">
-        <v>41</v>
+        <v>92</v>
       </c>
       <c r="F183" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="G183"/>
       <c r="H183" t="s">
-        <v>39</v>
+        <v>205</v>
       </c>
       <c r="I183" t="s">
         <v>230</v>
       </c>
       <c r="J183" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="K183" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="L183" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="M183"/>
       <c r="N183"/>
       <c r="O183" t="s">
-        <v>205</v>
+        <v>39</v>
       </c>
     </row>
     <row r="184">
@@ -15635,10 +15635,10 @@
         <v>144</v>
       </c>
       <c r="E184" t="s">
-        <v>45</v>
+        <v>8</v>
       </c>
       <c r="F184" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="G184"/>
       <c r="H184" t="s">
@@ -15674,10 +15674,10 @@
         <v>144</v>
       </c>
       <c r="E185" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="F185" t="n">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
       <c r="G185"/>
       <c r="H185" t="s">
@@ -15713,10 +15713,10 @@
         <v>144</v>
       </c>
       <c r="E186" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="F186" t="n">
-        <v>5.0</v>
+        <v>3.0</v>
       </c>
       <c r="G186"/>
       <c r="H186" t="s">
@@ -15752,10 +15752,10 @@
         <v>144</v>
       </c>
       <c r="E187" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="F187" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
       <c r="G187"/>
       <c r="H187" t="s">
@@ -15765,13 +15765,13 @@
         <v>230</v>
       </c>
       <c r="J187" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="K187" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="L187" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="M187"/>
       <c r="N187"/>
@@ -15791,10 +15791,10 @@
         <v>144</v>
       </c>
       <c r="E188" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="F188" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
       <c r="G188"/>
       <c r="H188" t="s">
@@ -15804,13 +15804,13 @@
         <v>230</v>
       </c>
       <c r="J188" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="K188" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="L188" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="M188"/>
       <c r="N188"/>
@@ -15830,10 +15830,10 @@
         <v>144</v>
       </c>
       <c r="E189" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="F189" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="G189"/>
       <c r="H189" t="s">
@@ -15869,10 +15869,10 @@
         <v>144</v>
       </c>
       <c r="E190" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="F190" t="n">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
       <c r="G190"/>
       <c r="H190" t="s">
@@ -15908,10 +15908,10 @@
         <v>144</v>
       </c>
       <c r="E191" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="F191" t="n">
-        <v>5.0</v>
+        <v>3.0</v>
       </c>
       <c r="G191"/>
       <c r="H191" t="s">
@@ -15947,10 +15947,10 @@
         <v>144</v>
       </c>
       <c r="E192" t="s">
-        <v>99</v>
+        <v>69</v>
       </c>
       <c r="F192" t="n">
-        <v>6.0</v>
+        <v>4.0</v>
       </c>
       <c r="G192"/>
       <c r="H192" t="s">
@@ -15986,10 +15986,10 @@
         <v>144</v>
       </c>
       <c r="E193" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="F193" t="n">
-        <v>7.0</v>
+        <v>5.0</v>
       </c>
       <c r="G193"/>
       <c r="H193" t="s">
@@ -16025,10 +16025,10 @@
         <v>144</v>
       </c>
       <c r="E194" t="s">
-        <v>87</v>
+        <v>104</v>
       </c>
       <c r="F194" t="n">
-        <v>1.0</v>
+        <v>6.0</v>
       </c>
       <c r="G194"/>
       <c r="H194" t="s">
@@ -16038,18 +16038,18 @@
         <v>230</v>
       </c>
       <c r="J194" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="K194" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="L194" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="M194"/>
       <c r="N194"/>
       <c r="O194" t="s">
-        <v>39</v>
+        <v>205</v>
       </c>
     </row>
     <row r="195">
@@ -16064,10 +16064,10 @@
         <v>144</v>
       </c>
       <c r="E195" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="F195" t="n">
-        <v>2.0</v>
+        <v>7.0</v>
       </c>
       <c r="G195"/>
       <c r="H195" t="s">
@@ -16077,18 +16077,18 @@
         <v>230</v>
       </c>
       <c r="J195" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="K195" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="L195" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="M195"/>
       <c r="N195"/>
       <c r="O195" t="s">
-        <v>39</v>
+        <v>205</v>
       </c>
     </row>
     <row r="196">
@@ -16103,10 +16103,10 @@
         <v>144</v>
       </c>
       <c r="E196" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="F196" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="G196"/>
       <c r="H196" t="s">
@@ -16142,10 +16142,10 @@
         <v>144</v>
       </c>
       <c r="E197" t="s">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="F197" t="n">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
       <c r="G197"/>
       <c r="H197" t="s">
@@ -16166,7 +16166,7 @@
       <c r="M197"/>
       <c r="N197"/>
       <c r="O197" t="s">
-        <v>205</v>
+        <v>39</v>
       </c>
     </row>
     <row r="198">
@@ -16178,13 +16178,13 @@
         <v>13</v>
       </c>
       <c r="D198" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="E198" t="s">
-        <v>8</v>
+        <v>92</v>
       </c>
       <c r="F198" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="G198"/>
       <c r="H198" t="s">
@@ -16194,18 +16194,18 @@
         <v>230</v>
       </c>
       <c r="J198" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="K198" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="L198" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="M198"/>
       <c r="N198"/>
       <c r="O198" t="s">
-        <v>205</v>
+        <v>39</v>
       </c>
     </row>
     <row r="199">
@@ -16220,10 +16220,10 @@
         <v>148</v>
       </c>
       <c r="E199" t="s">
-        <v>41</v>
+        <v>8</v>
       </c>
       <c r="F199" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G199"/>
       <c r="H199" t="s">
@@ -16259,10 +16259,10 @@
         <v>148</v>
       </c>
       <c r="E200" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="F200" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="G200"/>
       <c r="H200" t="s">
@@ -16298,10 +16298,10 @@
         <v>148</v>
       </c>
       <c r="E201" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="F201" t="n">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
       <c r="G201"/>
       <c r="H201" t="s">
@@ -16337,10 +16337,10 @@
         <v>148</v>
       </c>
       <c r="E202" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="F202" t="n">
-        <v>5.0</v>
+        <v>4.0</v>
       </c>
       <c r="G202"/>
       <c r="H202" t="s">
@@ -16376,10 +16376,10 @@
         <v>148</v>
       </c>
       <c r="E203" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="F203" t="n">
-        <v>1.0</v>
+        <v>5.0</v>
       </c>
       <c r="G203"/>
       <c r="H203" t="s">
@@ -16389,13 +16389,13 @@
         <v>230</v>
       </c>
       <c r="J203" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="K203" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="L203" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="M203"/>
       <c r="N203"/>
@@ -16415,10 +16415,10 @@
         <v>148</v>
       </c>
       <c r="E204" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="F204" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G204"/>
       <c r="H204" t="s">
@@ -16454,10 +16454,10 @@
         <v>148</v>
       </c>
       <c r="E205" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="F205" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="G205"/>
       <c r="H205" t="s">
@@ -16493,10 +16493,10 @@
         <v>148</v>
       </c>
       <c r="E206" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="F206" t="n">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
       <c r="G206"/>
       <c r="H206" t="s">
@@ -16532,10 +16532,10 @@
         <v>148</v>
       </c>
       <c r="E207" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="F207" t="n">
-        <v>5.0</v>
+        <v>4.0</v>
       </c>
       <c r="G207"/>
       <c r="H207" t="s">
@@ -16571,10 +16571,10 @@
         <v>148</v>
       </c>
       <c r="E208" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="F208" t="n">
-        <v>6.0</v>
+        <v>5.0</v>
       </c>
       <c r="G208"/>
       <c r="H208" t="s">
@@ -16610,10 +16610,10 @@
         <v>148</v>
       </c>
       <c r="E209" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="F209" t="n">
-        <v>1.0</v>
+        <v>6.0</v>
       </c>
       <c r="G209"/>
       <c r="H209" t="s">
@@ -16623,18 +16623,18 @@
         <v>230</v>
       </c>
       <c r="J209" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="K209" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="L209" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="M209"/>
       <c r="N209"/>
       <c r="O209" t="s">
-        <v>39</v>
+        <v>205</v>
       </c>
     </row>
     <row r="210">
@@ -16649,10 +16649,10 @@
         <v>148</v>
       </c>
       <c r="E210" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="F210" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G210"/>
       <c r="H210" t="s">
@@ -16688,10 +16688,10 @@
         <v>148</v>
       </c>
       <c r="E211" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="F211" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="G211"/>
       <c r="H211" t="s">
@@ -16727,10 +16727,10 @@
         <v>148</v>
       </c>
       <c r="E212" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="F212" t="n">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
       <c r="G212"/>
       <c r="H212" t="s">
@@ -16751,7 +16751,7 @@
       <c r="M212"/>
       <c r="N212"/>
       <c r="O212" t="s">
-        <v>205</v>
+        <v>39</v>
       </c>
     </row>
     <row r="213">
@@ -17195,7 +17195,7 @@
         <v>149</v>
       </c>
       <c r="E224" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F224" t="n">
         <v>1.0</v>
@@ -17273,7 +17273,7 @@
         <v>149</v>
       </c>
       <c r="E226" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F226" t="n">
         <v>3.0</v>
@@ -17702,7 +17702,7 @@
         <v>144</v>
       </c>
       <c r="E237" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="F237" t="n">
         <v>6.0</v>
@@ -17780,7 +17780,7 @@
         <v>144</v>
       </c>
       <c r="E239" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F239" t="n">
         <v>1.0</v>
@@ -17858,7 +17858,7 @@
         <v>144</v>
       </c>
       <c r="E241" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F241" t="n">
         <v>3.0</v>
@@ -18326,7 +18326,7 @@
         <v>148</v>
       </c>
       <c r="E253" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F253" t="n">
         <v>1.0</v>
@@ -18404,7 +18404,7 @@
         <v>148</v>
       </c>
       <c r="E255" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F255" t="n">
         <v>3.0</v>
@@ -18872,7 +18872,7 @@
         <v>149</v>
       </c>
       <c r="E267" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F267" t="n">
         <v>1.0</v>
@@ -18950,7 +18950,7 @@
         <v>149</v>
       </c>
       <c r="E269" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F269" t="n">
         <v>3.0</v>
@@ -19379,7 +19379,7 @@
         <v>144</v>
       </c>
       <c r="E280" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="F280" t="n">
         <v>6.0</v>
@@ -19457,7 +19457,7 @@
         <v>144</v>
       </c>
       <c r="E282" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F282" t="n">
         <v>1.0</v>
@@ -19535,7 +19535,7 @@
         <v>144</v>
       </c>
       <c r="E284" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F284" t="n">
         <v>3.0</v>
@@ -19574,7 +19574,7 @@
         <v>144</v>
       </c>
       <c r="E285" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="F285" t="n">
         <v>4.0</v>
@@ -20042,7 +20042,7 @@
         <v>148</v>
       </c>
       <c r="E297" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F297" t="n">
         <v>1.0</v>
@@ -20120,7 +20120,7 @@
         <v>148</v>
       </c>
       <c r="E299" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F299" t="n">
         <v>3.0</v>
@@ -20159,7 +20159,7 @@
         <v>148</v>
       </c>
       <c r="E300" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="F300" t="n">
         <v>4.0</v>
@@ -20627,7 +20627,7 @@
         <v>149</v>
       </c>
       <c r="E312" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F312" t="n">
         <v>1.0</v>
@@ -20705,7 +20705,7 @@
         <v>149</v>
       </c>
       <c r="E314" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F314" t="n">
         <v>3.0</v>
@@ -21134,7 +21134,7 @@
         <v>144</v>
       </c>
       <c r="E325" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="F325" t="n">
         <v>6.0</v>
@@ -21212,7 +21212,7 @@
         <v>144</v>
       </c>
       <c r="E327" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F327" t="n">
         <v>1.0</v>
@@ -21290,7 +21290,7 @@
         <v>144</v>
       </c>
       <c r="E329" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F329" t="n">
         <v>3.0</v>
@@ -21758,7 +21758,7 @@
         <v>148</v>
       </c>
       <c r="E341" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F341" t="n">
         <v>1.0</v>
@@ -21836,7 +21836,7 @@
         <v>148</v>
       </c>
       <c r="E343" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F343" t="n">
         <v>3.0</v>
@@ -22304,7 +22304,7 @@
         <v>149</v>
       </c>
       <c r="E355" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F355" t="n">
         <v>1.0</v>
@@ -22382,7 +22382,7 @@
         <v>149</v>
       </c>
       <c r="E357" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F357" t="n">
         <v>3.0</v>
@@ -22466,7 +22466,7 @@
       </c>
       <c r="B4"/>
       <c r="C4" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D4" t="s">
         <v>243</v>
@@ -22493,7 +22493,7 @@
       </c>
       <c r="B5"/>
       <c r="C5" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D5" t="s">
         <v>246</v>
@@ -22518,7 +22518,7 @@
       </c>
       <c r="B6"/>
       <c r="C6" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D6" t="s">
         <v>248</v>
@@ -22568,7 +22568,7 @@
       </c>
       <c r="B8"/>
       <c r="C8" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D8" t="s">
         <v>250</v>
@@ -22593,7 +22593,7 @@
       </c>
       <c r="B9"/>
       <c r="C9" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="D9" t="s">
         <v>251</v>
@@ -22618,7 +22618,7 @@
       </c>
       <c r="B10"/>
       <c r="C10" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D10" t="s">
         <v>252</v>
@@ -22643,7 +22643,7 @@
       </c>
       <c r="B11"/>
       <c r="C11" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D11" t="s">
         <v>253</v>
@@ -22722,7 +22722,9 @@
       <c r="G4" t="n">
         <v>1.0</v>
       </c>
-      <c r="H4"/>
+      <c r="H4" t="s">
+        <v>257</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n" s="29">
@@ -22736,7 +22738,7 @@
         <v>140</v>
       </c>
       <c r="E5" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="F5"/>
       <c r="G5" t="n">
@@ -22756,7 +22758,7 @@
         <v>141</v>
       </c>
       <c r="E6" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F6"/>
       <c r="G6" t="n">
@@ -22782,9 +22784,7 @@
       <c r="G7" t="n">
         <v>1.0</v>
       </c>
-      <c r="H7" t="s">
-        <v>259</v>
-      </c>
+      <c r="H7"/>
     </row>
     <row r="8">
       <c r="A8" t="n" s="29">
@@ -22798,7 +22798,7 @@
         <v>140</v>
       </c>
       <c r="E8" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="F8"/>
       <c r="G8" t="n">
@@ -22818,7 +22818,7 @@
         <v>141</v>
       </c>
       <c r="E9" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F9"/>
       <c r="G9" t="n">
@@ -22858,7 +22858,7 @@
         <v>140</v>
       </c>
       <c r="E11" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="F11"/>
       <c r="G11" t="n">
@@ -22878,7 +22878,7 @@
         <v>141</v>
       </c>
       <c r="E12" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F12"/>
       <c r="G12" t="n">
@@ -22918,7 +22918,7 @@
         <v>140</v>
       </c>
       <c r="E14" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="F14"/>
       <c r="G14" t="n">
@@ -22938,7 +22938,7 @@
         <v>141</v>
       </c>
       <c r="E15" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F15"/>
       <c r="G15" t="n">
@@ -22978,7 +22978,7 @@
         <v>140</v>
       </c>
       <c r="E17" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="F17"/>
       <c r="G17" t="n">
@@ -22998,7 +22998,7 @@
         <v>141</v>
       </c>
       <c r="E18" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F18"/>
       <c r="G18" t="n">
@@ -23038,7 +23038,7 @@
         <v>140</v>
       </c>
       <c r="E20" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="F20"/>
       <c r="G20" t="n">
@@ -23058,7 +23058,7 @@
         <v>141</v>
       </c>
       <c r="E21" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F21"/>
       <c r="G21" t="n">
@@ -23098,7 +23098,7 @@
         <v>140</v>
       </c>
       <c r="E23" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="F23"/>
       <c r="G23" t="n">
@@ -23118,7 +23118,7 @@
         <v>141</v>
       </c>
       <c r="E24" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F24"/>
       <c r="G24" t="n">
@@ -23158,7 +23158,7 @@
         <v>140</v>
       </c>
       <c r="E26" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="F26"/>
       <c r="G26" t="n">
@@ -23178,7 +23178,7 @@
         <v>141</v>
       </c>
       <c r="E27" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F27"/>
       <c r="G27" t="n">
@@ -23231,7 +23231,7 @@
         <v>134</v>
       </c>
       <c r="E4" t="s">
-        <v>261</v>
+        <v>133</v>
       </c>
     </row>
     <row r="5">
@@ -23261,7 +23261,7 @@
         <v>134</v>
       </c>
       <c r="E6" t="s">
-        <v>133</v>
+        <v>261</v>
       </c>
     </row>
     <row r="7">
@@ -23507,7 +23507,7 @@
         <v>23</v>
       </c>
       <c r="E4" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F4" t="s">
         <v>24</v>
@@ -23525,7 +23525,7 @@
         <v>23</v>
       </c>
       <c r="E5" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F5" t="s">
         <v>24</v>
@@ -23978,15 +23978,17 @@
         <v>87</v>
       </c>
       <c r="E16" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="F16" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="G16" t="s">
-        <v>90</v>
-      </c>
-      <c r="H16"/>
+        <v>86</v>
+      </c>
+      <c r="H16" t="s">
+        <v>38</v>
+      </c>
       <c r="I16" t="s">
         <v>39</v>
       </c>
@@ -24006,16 +24008,16 @@
         <v>7</v>
       </c>
       <c r="D17" t="s">
+        <v>88</v>
+      </c>
+      <c r="E17" t="s">
+        <v>89</v>
+      </c>
+      <c r="F17" t="s">
+        <v>90</v>
+      </c>
+      <c r="G17" t="s">
         <v>91</v>
-      </c>
-      <c r="E17" t="s">
-        <v>92</v>
-      </c>
-      <c r="F17" t="s">
-        <v>93</v>
-      </c>
-      <c r="G17" t="s">
-        <v>94</v>
       </c>
       <c r="H17"/>
       <c r="I17" t="s">
@@ -24037,16 +24039,16 @@
         <v>7</v>
       </c>
       <c r="D18" t="s">
+        <v>92</v>
+      </c>
+      <c r="E18" t="s">
+        <v>93</v>
+      </c>
+      <c r="F18" t="s">
+        <v>94</v>
+      </c>
+      <c r="G18" t="s">
         <v>95</v>
-      </c>
-      <c r="E18" t="s">
-        <v>96</v>
-      </c>
-      <c r="F18" t="s">
-        <v>97</v>
-      </c>
-      <c r="G18" t="s">
-        <v>98</v>
       </c>
       <c r="H18"/>
       <c r="I18" t="s">
@@ -24068,20 +24070,18 @@
         <v>7</v>
       </c>
       <c r="D19" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="E19" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="F19" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="G19" t="s">
-        <v>102</v>
-      </c>
-      <c r="H19" t="s">
-        <v>103</v>
-      </c>
+        <v>95</v>
+      </c>
+      <c r="H19"/>
       <c r="I19" t="s">
         <v>39</v>
       </c>
@@ -24101,16 +24101,16 @@
         <v>7</v>
       </c>
       <c r="D20" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="E20" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="F20" t="s">
-        <v>106</v>
+        <v>94</v>
       </c>
       <c r="G20" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
       <c r="H20"/>
       <c r="I20" t="s">
@@ -24129,19 +24129,19 @@
       </c>
       <c r="B21"/>
       <c r="C21" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D21" t="s">
-        <v>8</v>
+        <v>100</v>
       </c>
       <c r="E21" t="s">
-        <v>36</v>
+        <v>101</v>
       </c>
       <c r="F21" t="s">
-        <v>37</v>
+        <v>102</v>
       </c>
       <c r="G21" t="s">
-        <v>38</v>
+        <v>103</v>
       </c>
       <c r="H21"/>
       <c r="I21" t="s">
@@ -24160,21 +24160,23 @@
       </c>
       <c r="B22"/>
       <c r="C22" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D22" t="s">
-        <v>41</v>
+        <v>104</v>
       </c>
       <c r="E22" t="s">
-        <v>42</v>
+        <v>105</v>
       </c>
       <c r="F22" t="s">
-        <v>43</v>
+        <v>106</v>
       </c>
       <c r="G22" t="s">
-        <v>44</v>
-      </c>
-      <c r="H22"/>
+        <v>107</v>
+      </c>
+      <c r="H22" t="s">
+        <v>108</v>
+      </c>
       <c r="I22" t="s">
         <v>39</v>
       </c>
@@ -24191,19 +24193,19 @@
       </c>
       <c r="B23"/>
       <c r="C23" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D23" t="s">
-        <v>45</v>
+        <v>109</v>
       </c>
       <c r="E23" t="s">
-        <v>46</v>
+        <v>110</v>
       </c>
       <c r="F23" t="s">
-        <v>47</v>
+        <v>111</v>
       </c>
       <c r="G23" t="s">
-        <v>48</v>
+        <v>112</v>
       </c>
       <c r="H23"/>
       <c r="I23" t="s">
@@ -24225,16 +24227,16 @@
         <v>10</v>
       </c>
       <c r="D24" t="s">
-        <v>49</v>
+        <v>8</v>
       </c>
       <c r="E24" t="s">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="F24" t="s">
-        <v>51</v>
+        <v>37</v>
       </c>
       <c r="G24" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="H24"/>
       <c r="I24" t="s">
@@ -24256,16 +24258,16 @@
         <v>10</v>
       </c>
       <c r="D25" t="s">
-        <v>53</v>
+        <v>41</v>
       </c>
       <c r="E25" t="s">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="F25" t="s">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="G25" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="H25"/>
       <c r="I25" t="s">
@@ -24287,16 +24289,16 @@
         <v>10</v>
       </c>
       <c r="D26" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="E26" t="s">
-        <v>58</v>
+        <v>46</v>
       </c>
       <c r="F26" t="s">
-        <v>59</v>
+        <v>47</v>
       </c>
       <c r="G26" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="H26"/>
       <c r="I26" t="s">
@@ -24318,16 +24320,16 @@
         <v>10</v>
       </c>
       <c r="D27" t="s">
-        <v>61</v>
+        <v>49</v>
       </c>
       <c r="E27" t="s">
-        <v>62</v>
+        <v>50</v>
       </c>
       <c r="F27" t="s">
-        <v>63</v>
+        <v>51</v>
       </c>
       <c r="G27" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="H27"/>
       <c r="I27" t="s">
@@ -24349,16 +24351,16 @@
         <v>10</v>
       </c>
       <c r="D28" t="s">
-        <v>65</v>
+        <v>53</v>
       </c>
       <c r="E28" t="s">
-        <v>66</v>
+        <v>54</v>
       </c>
       <c r="F28" t="s">
-        <v>67</v>
+        <v>55</v>
       </c>
       <c r="G28" t="s">
-        <v>68</v>
+        <v>56</v>
       </c>
       <c r="H28"/>
       <c r="I28" t="s">
@@ -24380,16 +24382,16 @@
         <v>10</v>
       </c>
       <c r="D29" t="s">
-        <v>69</v>
+        <v>57</v>
       </c>
       <c r="E29" t="s">
-        <v>70</v>
+        <v>58</v>
       </c>
       <c r="F29" t="s">
-        <v>71</v>
+        <v>59</v>
       </c>
       <c r="G29" t="s">
-        <v>72</v>
+        <v>60</v>
       </c>
       <c r="H29"/>
       <c r="I29" t="s">
@@ -24411,20 +24413,18 @@
         <v>10</v>
       </c>
       <c r="D30" t="s">
-        <v>73</v>
+        <v>61</v>
       </c>
       <c r="E30" t="s">
-        <v>74</v>
+        <v>62</v>
       </c>
       <c r="F30" t="s">
-        <v>75</v>
+        <v>63</v>
       </c>
       <c r="G30" t="s">
-        <v>76</v>
-      </c>
-      <c r="H30" t="s">
-        <v>77</v>
-      </c>
+        <v>64</v>
+      </c>
+      <c r="H30"/>
       <c r="I30" t="s">
         <v>39</v>
       </c>
@@ -24444,20 +24444,18 @@
         <v>10</v>
       </c>
       <c r="D31" t="s">
-        <v>78</v>
+        <v>65</v>
       </c>
       <c r="E31" t="s">
-        <v>79</v>
+        <v>66</v>
       </c>
       <c r="F31" t="s">
-        <v>80</v>
+        <v>67</v>
       </c>
       <c r="G31" t="s">
-        <v>81</v>
-      </c>
-      <c r="H31" t="s">
-        <v>82</v>
-      </c>
+        <v>68</v>
+      </c>
+      <c r="H31"/>
       <c r="I31" t="s">
         <v>39</v>
       </c>
@@ -24477,20 +24475,18 @@
         <v>10</v>
       </c>
       <c r="D32" t="s">
-        <v>83</v>
+        <v>69</v>
       </c>
       <c r="E32" t="s">
-        <v>84</v>
+        <v>70</v>
       </c>
       <c r="F32" t="s">
-        <v>85</v>
+        <v>71</v>
       </c>
       <c r="G32" t="s">
-        <v>86</v>
-      </c>
-      <c r="H32" t="s">
-        <v>38</v>
-      </c>
+        <v>72</v>
+      </c>
+      <c r="H32"/>
       <c r="I32" t="s">
         <v>39</v>
       </c>
@@ -24510,19 +24506,19 @@
         <v>10</v>
       </c>
       <c r="D33" t="s">
-        <v>108</v>
+        <v>73</v>
       </c>
       <c r="E33" t="s">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="F33" t="s">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="G33" t="s">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="H33" t="s">
-        <v>38</v>
+        <v>77</v>
       </c>
       <c r="I33" t="s">
         <v>39</v>
@@ -24543,18 +24539,20 @@
         <v>10</v>
       </c>
       <c r="D34" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="E34" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="F34" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="G34" t="s">
-        <v>90</v>
-      </c>
-      <c r="H34"/>
+        <v>81</v>
+      </c>
+      <c r="H34" t="s">
+        <v>82</v>
+      </c>
       <c r="I34" t="s">
         <v>39</v>
       </c>
@@ -24574,18 +24572,20 @@
         <v>10</v>
       </c>
       <c r="D35" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="E35" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="F35" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="G35" t="s">
-        <v>94</v>
-      </c>
-      <c r="H35"/>
+        <v>86</v>
+      </c>
+      <c r="H35" t="s">
+        <v>38</v>
+      </c>
       <c r="I35" t="s">
         <v>39</v>
       </c>
@@ -24605,16 +24605,16 @@
         <v>10</v>
       </c>
       <c r="D36" t="s">
-        <v>109</v>
+        <v>88</v>
       </c>
       <c r="E36" t="s">
-        <v>110</v>
+        <v>89</v>
       </c>
       <c r="F36" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="G36" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="H36"/>
       <c r="I36" t="s">
@@ -24636,16 +24636,16 @@
         <v>10</v>
       </c>
       <c r="D37" t="s">
-        <v>111</v>
+        <v>92</v>
       </c>
       <c r="E37" t="s">
-        <v>112</v>
+        <v>93</v>
       </c>
       <c r="F37" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="G37" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="H37"/>
       <c r="I37" t="s">
@@ -24667,18 +24667,20 @@
         <v>10</v>
       </c>
       <c r="D38" t="s">
-        <v>95</v>
+        <v>104</v>
       </c>
       <c r="E38" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="F38" t="s">
-        <v>97</v>
+        <v>106</v>
       </c>
       <c r="G38" t="s">
-        <v>98</v>
-      </c>
-      <c r="H38"/>
+        <v>107</v>
+      </c>
+      <c r="H38" t="s">
+        <v>108</v>
+      </c>
       <c r="I38" t="s">
         <v>39</v>
       </c>
@@ -24698,20 +24700,18 @@
         <v>10</v>
       </c>
       <c r="D39" t="s">
-        <v>99</v>
+        <v>109</v>
       </c>
       <c r="E39" t="s">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="F39" t="s">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="G39" t="s">
-        <v>102</v>
-      </c>
-      <c r="H39" t="s">
-        <v>103</v>
-      </c>
+        <v>112</v>
+      </c>
+      <c r="H39"/>
       <c r="I39" t="s">
         <v>39</v>
       </c>
@@ -24728,19 +24728,19 @@
       </c>
       <c r="B40"/>
       <c r="C40" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D40" t="s">
-        <v>104</v>
+        <v>8</v>
       </c>
       <c r="E40" t="s">
-        <v>105</v>
+        <v>36</v>
       </c>
       <c r="F40" t="s">
-        <v>106</v>
+        <v>37</v>
       </c>
       <c r="G40" t="s">
-        <v>107</v>
+        <v>38</v>
       </c>
       <c r="H40"/>
       <c r="I40" t="s">
@@ -24762,16 +24762,16 @@
         <v>11</v>
       </c>
       <c r="D41" t="s">
-        <v>8</v>
+        <v>41</v>
       </c>
       <c r="E41" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="F41" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="G41" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="H41"/>
       <c r="I41" t="s">
@@ -24793,16 +24793,16 @@
         <v>11</v>
       </c>
       <c r="D42" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="E42" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="F42" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="G42" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="H42"/>
       <c r="I42" t="s">
@@ -24824,16 +24824,16 @@
         <v>11</v>
       </c>
       <c r="D43" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="E43" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="F43" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="G43" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="H43"/>
       <c r="I43" t="s">
@@ -24855,16 +24855,16 @@
         <v>11</v>
       </c>
       <c r="D44" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="E44" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="F44" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="G44" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="H44"/>
       <c r="I44" t="s">
@@ -24886,16 +24886,16 @@
         <v>11</v>
       </c>
       <c r="D45" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="E45" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="F45" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="G45" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="H45"/>
       <c r="I45" t="s">
@@ -24917,16 +24917,16 @@
         <v>11</v>
       </c>
       <c r="D46" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="E46" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="F46" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="G46" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="H46"/>
       <c r="I46" t="s">
@@ -24948,16 +24948,16 @@
         <v>11</v>
       </c>
       <c r="D47" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="E47" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="F47" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="G47" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="H47"/>
       <c r="I47" t="s">
@@ -24979,16 +24979,16 @@
         <v>11</v>
       </c>
       <c r="D48" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="E48" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="F48" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="G48" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="H48"/>
       <c r="I48" t="s">
@@ -25010,18 +25010,20 @@
         <v>11</v>
       </c>
       <c r="D49" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="E49" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="F49" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="G49" t="s">
-        <v>72</v>
-      </c>
-      <c r="H49"/>
+        <v>76</v>
+      </c>
+      <c r="H49" t="s">
+        <v>77</v>
+      </c>
       <c r="I49" t="s">
         <v>39</v>
       </c>
@@ -25041,19 +25043,19 @@
         <v>11</v>
       </c>
       <c r="D50" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="E50" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="F50" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G50" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="H50" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="I50" t="s">
         <v>39</v>
@@ -25074,19 +25076,19 @@
         <v>11</v>
       </c>
       <c r="D51" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="E51" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="F51" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="G51" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="H51" t="s">
-        <v>82</v>
+        <v>38</v>
       </c>
       <c r="I51" t="s">
         <v>39</v>
@@ -25107,20 +25109,18 @@
         <v>11</v>
       </c>
       <c r="D52" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="E52" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="F52" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="G52" t="s">
-        <v>86</v>
-      </c>
-      <c r="H52" t="s">
-        <v>38</v>
-      </c>
+        <v>91</v>
+      </c>
+      <c r="H52"/>
       <c r="I52" t="s">
         <v>39</v>
       </c>
@@ -25140,16 +25140,16 @@
         <v>11</v>
       </c>
       <c r="D53" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="E53" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="F53" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="G53" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="H53"/>
       <c r="I53" t="s">
@@ -25171,16 +25171,16 @@
         <v>11</v>
       </c>
       <c r="D54" t="s">
-        <v>91</v>
+        <v>100</v>
       </c>
       <c r="E54" t="s">
-        <v>92</v>
+        <v>101</v>
       </c>
       <c r="F54" t="s">
-        <v>93</v>
+        <v>102</v>
       </c>
       <c r="G54" t="s">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="H54"/>
       <c r="I54" t="s">
@@ -25202,19 +25202,19 @@
         <v>11</v>
       </c>
       <c r="D55" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="E55" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="F55" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="G55" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="H55" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="I55" t="s">
         <v>39</v>
@@ -25235,16 +25235,16 @@
         <v>11</v>
       </c>
       <c r="D56" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="E56" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="F56" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="G56" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="H56"/>
       <c r="I56" t="s">
@@ -25644,16 +25644,16 @@
         <v>12</v>
       </c>
       <c r="D69" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E69" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F69" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G69" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H69"/>
       <c r="I69" t="s">
@@ -25675,16 +25675,16 @@
         <v>12</v>
       </c>
       <c r="D70" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E70" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F70" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="G70" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H70"/>
       <c r="I70" t="s">
@@ -25706,20 +25706,18 @@
         <v>12</v>
       </c>
       <c r="D71" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E71" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F71" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G71" t="s">
-        <v>102</v>
-      </c>
-      <c r="H71" t="s">
         <v>103</v>
       </c>
+      <c r="H71"/>
       <c r="I71" t="s">
         <v>39</v>
       </c>
@@ -25750,7 +25748,9 @@
       <c r="G72" t="s">
         <v>107</v>
       </c>
-      <c r="H72"/>
+      <c r="H72" t="s">
+        <v>108</v>
+      </c>
       <c r="I72" t="s">
         <v>39</v>
       </c>
@@ -25767,19 +25767,19 @@
       </c>
       <c r="B73"/>
       <c r="C73" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D73" t="s">
-        <v>8</v>
+        <v>109</v>
       </c>
       <c r="E73" t="s">
-        <v>36</v>
+        <v>110</v>
       </c>
       <c r="F73" t="s">
-        <v>37</v>
+        <v>111</v>
       </c>
       <c r="G73" t="s">
-        <v>38</v>
+        <v>112</v>
       </c>
       <c r="H73"/>
       <c r="I73" t="s">
@@ -25801,16 +25801,16 @@
         <v>13</v>
       </c>
       <c r="D74" t="s">
-        <v>41</v>
+        <v>8</v>
       </c>
       <c r="E74" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="F74" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="G74" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="H74"/>
       <c r="I74" t="s">
@@ -25832,16 +25832,16 @@
         <v>13</v>
       </c>
       <c r="D75" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="E75" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="F75" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G75" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H75"/>
       <c r="I75" t="s">
@@ -25863,16 +25863,16 @@
         <v>13</v>
       </c>
       <c r="D76" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="E76" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="F76" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G76" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H76"/>
       <c r="I76" t="s">
@@ -25894,16 +25894,16 @@
         <v>13</v>
       </c>
       <c r="D77" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="E77" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="F77" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="G77" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="H77"/>
       <c r="I77" t="s">
@@ -25925,16 +25925,16 @@
         <v>13</v>
       </c>
       <c r="D78" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="E78" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="F78" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="G78" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="H78"/>
       <c r="I78" t="s">
@@ -25956,16 +25956,16 @@
         <v>13</v>
       </c>
       <c r="D79" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="E79" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="F79" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="G79" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="H79"/>
       <c r="I79" t="s">
@@ -25987,16 +25987,16 @@
         <v>13</v>
       </c>
       <c r="D80" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="E80" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="F80" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="G80" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="H80"/>
       <c r="I80" t="s">
@@ -26018,16 +26018,16 @@
         <v>13</v>
       </c>
       <c r="D81" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="E81" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="F81" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="G81" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="H81"/>
       <c r="I81" t="s">
@@ -26049,20 +26049,18 @@
         <v>13</v>
       </c>
       <c r="D82" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="E82" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="F82" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="G82" t="s">
-        <v>76</v>
-      </c>
-      <c r="H82" t="s">
-        <v>77</v>
-      </c>
+        <v>72</v>
+      </c>
+      <c r="H82"/>
       <c r="I82" t="s">
         <v>39</v>
       </c>
@@ -26082,19 +26080,19 @@
         <v>13</v>
       </c>
       <c r="D83" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="E83" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="F83" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G83" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="H83" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="I83" t="s">
         <v>39</v>
@@ -26115,19 +26113,19 @@
         <v>13</v>
       </c>
       <c r="D84" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="E84" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="F84" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="G84" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="H84" t="s">
-        <v>38</v>
+        <v>82</v>
       </c>
       <c r="I84" t="s">
         <v>39</v>
@@ -26148,18 +26146,20 @@
         <v>13</v>
       </c>
       <c r="D85" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="E85" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="F85" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="G85" t="s">
-        <v>90</v>
-      </c>
-      <c r="H85"/>
+        <v>86</v>
+      </c>
+      <c r="H85" t="s">
+        <v>38</v>
+      </c>
       <c r="I85" t="s">
         <v>39</v>
       </c>
@@ -26179,16 +26179,16 @@
         <v>13</v>
       </c>
       <c r="D86" t="s">
+        <v>88</v>
+      </c>
+      <c r="E86" t="s">
+        <v>89</v>
+      </c>
+      <c r="F86" t="s">
+        <v>90</v>
+      </c>
+      <c r="G86" t="s">
         <v>91</v>
-      </c>
-      <c r="E86" t="s">
-        <v>92</v>
-      </c>
-      <c r="F86" t="s">
-        <v>93</v>
-      </c>
-      <c r="G86" t="s">
-        <v>94</v>
       </c>
       <c r="H86"/>
       <c r="I86" t="s">
@@ -26210,16 +26210,16 @@
         <v>13</v>
       </c>
       <c r="D87" t="s">
+        <v>92</v>
+      </c>
+      <c r="E87" t="s">
+        <v>93</v>
+      </c>
+      <c r="F87" t="s">
+        <v>94</v>
+      </c>
+      <c r="G87" t="s">
         <v>95</v>
-      </c>
-      <c r="E87" t="s">
-        <v>96</v>
-      </c>
-      <c r="F87" t="s">
-        <v>97</v>
-      </c>
-      <c r="G87" t="s">
-        <v>98</v>
       </c>
       <c r="H87"/>
       <c r="I87" t="s">
@@ -26241,19 +26241,19 @@
         <v>13</v>
       </c>
       <c r="D88" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="E88" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="F88" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="G88" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="H88" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="I88" t="s">
         <v>39</v>
@@ -26274,16 +26274,16 @@
         <v>13</v>
       </c>
       <c r="D89" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="E89" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="F89" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="G89" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="H89"/>
       <c r="I89" t="s">
@@ -26683,16 +26683,16 @@
         <v>14</v>
       </c>
       <c r="D102" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E102" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F102" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G102" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H102"/>
       <c r="I102" t="s">
@@ -26714,16 +26714,16 @@
         <v>14</v>
       </c>
       <c r="D103" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E103" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F103" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="G103" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H103"/>
       <c r="I103" t="s">
@@ -26745,19 +26745,19 @@
         <v>14</v>
       </c>
       <c r="D104" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="E104" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="F104" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="G104" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="H104" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="I104" t="s">
         <v>39</v>
@@ -26778,16 +26778,16 @@
         <v>14</v>
       </c>
       <c r="D105" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="E105" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="F105" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="G105" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="H105"/>
       <c r="I105" t="s">
@@ -27187,16 +27187,16 @@
         <v>15</v>
       </c>
       <c r="D118" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E118" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F118" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G118" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H118"/>
       <c r="I118" t="s">
@@ -27218,16 +27218,16 @@
         <v>15</v>
       </c>
       <c r="D119" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E119" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F119" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="G119" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H119"/>
       <c r="I119" t="s">
@@ -27249,16 +27249,16 @@
         <v>15</v>
       </c>
       <c r="D120" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="E120" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="F120" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="G120" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="H120"/>
       <c r="I120" t="s">
@@ -27280,19 +27280,19 @@
         <v>15</v>
       </c>
       <c r="D121" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="E121" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="F121" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="G121" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="H121" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="I121" t="s">
         <v>39</v>
@@ -27313,16 +27313,16 @@
         <v>15</v>
       </c>
       <c r="D122" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="E122" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="F122" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="G122" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="H122"/>
       <c r="I122" t="s">
@@ -27722,16 +27722,16 @@
         <v>16</v>
       </c>
       <c r="D135" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E135" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F135" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G135" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H135"/>
       <c r="I135" t="s">
@@ -27753,16 +27753,16 @@
         <v>16</v>
       </c>
       <c r="D136" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E136" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F136" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="G136" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H136"/>
       <c r="I136" t="s">
@@ -27784,19 +27784,19 @@
         <v>16</v>
       </c>
       <c r="D137" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="E137" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="F137" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="G137" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="H137" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="I137" t="s">
         <v>39</v>
@@ -27817,16 +27817,16 @@
         <v>16</v>
       </c>
       <c r="D138" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="E138" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="F138" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="G138" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="H138"/>
       <c r="I138" t="s">
@@ -27967,7 +27967,7 @@
       </c>
       <c r="B6"/>
       <c r="C6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D6" t="s">
         <v>122</v>
@@ -27997,7 +27997,7 @@
       </c>
       <c r="B7"/>
       <c r="C7" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D7" t="s">
         <v>124</v>
@@ -28027,7 +28027,7 @@
       </c>
       <c r="B8"/>
       <c r="C8" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D8" t="s">
         <v>125</v>
@@ -28057,7 +28057,7 @@
       </c>
       <c r="B9"/>
       <c r="C9" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D9" t="s">
         <v>126</v>
@@ -28087,7 +28087,7 @@
       </c>
       <c r="B10"/>
       <c r="C10" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D10" t="s">
         <v>127</v>
@@ -28119,7 +28119,7 @@
       </c>
       <c r="B11"/>
       <c r="C11" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D11" t="s">
         <v>129</v>
@@ -28191,7 +28191,7 @@
         <v>7</v>
       </c>
       <c r="D4" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E4" t="s">
         <v>122</v>
@@ -28212,7 +28212,7 @@
         <v>7</v>
       </c>
       <c r="D5" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E5" t="s">
         <v>127</v>
@@ -28233,7 +28233,7 @@
         <v>7</v>
       </c>
       <c r="D6" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E6" t="s">
         <v>129</v>
@@ -28254,7 +28254,7 @@
         <v>7</v>
       </c>
       <c r="D7" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E7" t="s">
         <v>122</v>
@@ -28275,7 +28275,7 @@
         <v>7</v>
       </c>
       <c r="D8" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E8" t="s">
         <v>127</v>
@@ -28296,7 +28296,7 @@
         <v>7</v>
       </c>
       <c r="D9" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E9" t="s">
         <v>129</v>
@@ -28314,13 +28314,13 @@
       </c>
       <c r="B10"/>
       <c r="C10" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D10" t="s">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="E10" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="F10" t="s">
         <v>134</v>
@@ -28335,19 +28335,19 @@
       </c>
       <c r="B11"/>
       <c r="C11" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D11" t="s">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="E11" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="F11" t="s">
         <v>134</v>
       </c>
       <c r="G11" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="12">
@@ -28356,19 +28356,19 @@
       </c>
       <c r="B12"/>
       <c r="C12" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D12" t="s">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="E12" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="F12" t="s">
         <v>134</v>
       </c>
       <c r="G12" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
     </row>
     <row r="13">
@@ -28380,13 +28380,13 @@
         <v>10</v>
       </c>
       <c r="D13" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E13" t="s">
         <v>122</v>
       </c>
       <c r="F13" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="G13" t="s">
         <v>133</v>
@@ -28401,13 +28401,13 @@
         <v>10</v>
       </c>
       <c r="D14" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E14" t="s">
         <v>127</v>
       </c>
       <c r="F14" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="G14" t="s">
         <v>133</v>
@@ -28422,13 +28422,13 @@
         <v>10</v>
       </c>
       <c r="D15" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E15" t="s">
         <v>129</v>
       </c>
       <c r="F15" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="G15" t="s">
         <v>133</v>
@@ -28443,13 +28443,13 @@
         <v>10</v>
       </c>
       <c r="D16" t="s">
-        <v>111</v>
+        <v>88</v>
       </c>
       <c r="E16" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="F16" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="G16" t="s">
         <v>133</v>
@@ -28464,16 +28464,16 @@
         <v>10</v>
       </c>
       <c r="D17" t="s">
-        <v>111</v>
+        <v>88</v>
       </c>
       <c r="E17" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="F17" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="G17" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
     </row>
     <row r="18">
@@ -28485,16 +28485,16 @@
         <v>10</v>
       </c>
       <c r="D18" t="s">
-        <v>111</v>
+        <v>88</v>
       </c>
       <c r="E18" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="F18" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="G18" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
     </row>
     <row r="19">
@@ -28506,7 +28506,7 @@
         <v>11</v>
       </c>
       <c r="D19" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E19" t="s">
         <v>122</v>
@@ -28527,7 +28527,7 @@
         <v>11</v>
       </c>
       <c r="D20" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E20" t="s">
         <v>127</v>
@@ -28548,7 +28548,7 @@
         <v>11</v>
       </c>
       <c r="D21" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E21" t="s">
         <v>129</v>
@@ -28569,7 +28569,7 @@
         <v>11</v>
       </c>
       <c r="D22" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E22" t="s">
         <v>122</v>
@@ -28590,7 +28590,7 @@
         <v>11</v>
       </c>
       <c r="D23" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E23" t="s">
         <v>127</v>
@@ -28611,7 +28611,7 @@
         <v>11</v>
       </c>
       <c r="D24" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E24" t="s">
         <v>129</v>
@@ -28632,7 +28632,7 @@
         <v>12</v>
       </c>
       <c r="D25" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E25" t="s">
         <v>122</v>
@@ -28653,7 +28653,7 @@
         <v>12</v>
       </c>
       <c r="D26" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E26" t="s">
         <v>127</v>
@@ -28674,7 +28674,7 @@
         <v>12</v>
       </c>
       <c r="D27" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E27" t="s">
         <v>129</v>
@@ -28695,7 +28695,7 @@
         <v>12</v>
       </c>
       <c r="D28" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E28" t="s">
         <v>122</v>
@@ -28716,7 +28716,7 @@
         <v>12</v>
       </c>
       <c r="D29" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E29" t="s">
         <v>127</v>
@@ -28737,7 +28737,7 @@
         <v>12</v>
       </c>
       <c r="D30" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E30" t="s">
         <v>129</v>
@@ -28758,7 +28758,7 @@
         <v>13</v>
       </c>
       <c r="D31" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E31" t="s">
         <v>122</v>
@@ -28779,7 +28779,7 @@
         <v>13</v>
       </c>
       <c r="D32" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E32" t="s">
         <v>127</v>
@@ -28800,7 +28800,7 @@
         <v>13</v>
       </c>
       <c r="D33" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E33" t="s">
         <v>129</v>
@@ -28821,7 +28821,7 @@
         <v>13</v>
       </c>
       <c r="D34" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E34" t="s">
         <v>122</v>
@@ -28842,7 +28842,7 @@
         <v>13</v>
       </c>
       <c r="D35" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E35" t="s">
         <v>127</v>
@@ -28863,7 +28863,7 @@
         <v>13</v>
       </c>
       <c r="D36" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E36" t="s">
         <v>129</v>
@@ -28884,7 +28884,7 @@
         <v>14</v>
       </c>
       <c r="D37" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E37" t="s">
         <v>122</v>
@@ -28905,7 +28905,7 @@
         <v>14</v>
       </c>
       <c r="D38" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E38" t="s">
         <v>127</v>
@@ -28926,7 +28926,7 @@
         <v>14</v>
       </c>
       <c r="D39" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E39" t="s">
         <v>129</v>
@@ -28947,7 +28947,7 @@
         <v>14</v>
       </c>
       <c r="D40" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E40" t="s">
         <v>122</v>
@@ -28968,7 +28968,7 @@
         <v>14</v>
       </c>
       <c r="D41" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E41" t="s">
         <v>127</v>
@@ -28989,7 +28989,7 @@
         <v>14</v>
       </c>
       <c r="D42" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E42" t="s">
         <v>129</v>
@@ -29010,7 +29010,7 @@
         <v>15</v>
       </c>
       <c r="D43" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E43" t="s">
         <v>122</v>
@@ -29031,7 +29031,7 @@
         <v>15</v>
       </c>
       <c r="D44" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E44" t="s">
         <v>127</v>
@@ -29052,7 +29052,7 @@
         <v>15</v>
       </c>
       <c r="D45" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E45" t="s">
         <v>129</v>
@@ -29073,7 +29073,7 @@
         <v>15</v>
       </c>
       <c r="D46" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E46" t="s">
         <v>122</v>
@@ -29094,7 +29094,7 @@
         <v>15</v>
       </c>
       <c r="D47" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E47" t="s">
         <v>127</v>
@@ -29115,7 +29115,7 @@
         <v>15</v>
       </c>
       <c r="D48" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E48" t="s">
         <v>129</v>
@@ -29136,7 +29136,7 @@
         <v>16</v>
       </c>
       <c r="D49" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E49" t="s">
         <v>122</v>
@@ -29157,7 +29157,7 @@
         <v>16</v>
       </c>
       <c r="D50" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E50" t="s">
         <v>127</v>
@@ -29178,7 +29178,7 @@
         <v>16</v>
       </c>
       <c r="D51" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E51" t="s">
         <v>129</v>
@@ -29199,7 +29199,7 @@
         <v>16</v>
       </c>
       <c r="D52" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E52" t="s">
         <v>122</v>
@@ -29220,7 +29220,7 @@
         <v>16</v>
       </c>
       <c r="D53" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E53" t="s">
         <v>127</v>
@@ -29241,7 +29241,7 @@
         <v>16</v>
       </c>
       <c r="D54" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E54" t="s">
         <v>129</v>
@@ -32253,7 +32253,7 @@
         <v>2.0</v>
       </c>
       <c r="H14" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="I14" t="n">
         <v>6.0</v>
@@ -32307,7 +32307,7 @@
         <v>3.0</v>
       </c>
       <c r="H16" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="I16" t="n">
         <v>1.0</v>
@@ -32361,10 +32361,10 @@
         <v>3.0</v>
       </c>
       <c r="H18" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="I18" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="19">
@@ -32388,10 +32388,10 @@
         <v>3.0</v>
       </c>
       <c r="H19" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="I19" t="n">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="20">
@@ -32406,19 +32406,19 @@
         <v>156</v>
       </c>
       <c r="E20" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="F20" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="G20" t="n">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
       <c r="H20" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="I20" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="21">
@@ -32427,25 +32427,25 @@
       </c>
       <c r="B21"/>
       <c r="C21" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D21" t="s">
         <v>156</v>
       </c>
       <c r="E21" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="F21" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="G21" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="H21" t="s">
-        <v>8</v>
+        <v>100</v>
       </c>
       <c r="I21" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="22">
@@ -32454,25 +32454,25 @@
       </c>
       <c r="B22"/>
       <c r="C22" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D22" t="s">
         <v>156</v>
       </c>
       <c r="E22" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
       <c r="F22" t="s">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="G22" t="n">
+        <v>4.0</v>
+      </c>
+      <c r="H22" t="s">
+        <v>109</v>
+      </c>
+      <c r="I22" t="n">
         <v>1.0</v>
-      </c>
-      <c r="H22" t="s">
-        <v>41</v>
-      </c>
-      <c r="I22" t="n">
-        <v>2.0</v>
       </c>
     </row>
     <row r="23">
@@ -32496,10 +32496,10 @@
         <v>1.0</v>
       </c>
       <c r="H23" t="s">
-        <v>45</v>
+        <v>8</v>
       </c>
       <c r="I23" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="24">
@@ -32523,10 +32523,10 @@
         <v>1.0</v>
       </c>
       <c r="H24" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="I24" t="n">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="25">
@@ -32550,10 +32550,10 @@
         <v>1.0</v>
       </c>
       <c r="H25" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="I25" t="n">
-        <v>5.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="26">
@@ -32568,19 +32568,19 @@
         <v>156</v>
       </c>
       <c r="E26" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="F26" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="G26" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="H26" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="I26" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="27">
@@ -32595,19 +32595,19 @@
         <v>156</v>
       </c>
       <c r="E27" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="F27" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="G27" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="H27" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="I27" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="28">
@@ -32631,10 +32631,10 @@
         <v>2.0</v>
       </c>
       <c r="H28" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="I28" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="29">
@@ -32658,10 +32658,10 @@
         <v>2.0</v>
       </c>
       <c r="H29" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="I29" t="n">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="30">
@@ -32685,10 +32685,10 @@
         <v>2.0</v>
       </c>
       <c r="H30" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="I30" t="n">
-        <v>5.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="31">
@@ -32712,10 +32712,10 @@
         <v>2.0</v>
       </c>
       <c r="H31" t="s">
-        <v>99</v>
+        <v>69</v>
       </c>
       <c r="I31" t="n">
-        <v>6.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="32">
@@ -32739,10 +32739,10 @@
         <v>2.0</v>
       </c>
       <c r="H32" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="I32" t="n">
-        <v>7.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="33">
@@ -32757,19 +32757,19 @@
         <v>156</v>
       </c>
       <c r="E33" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="F33" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="G33" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="H33" t="s">
-        <v>87</v>
+        <v>104</v>
       </c>
       <c r="I33" t="n">
-        <v>1.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="34">
@@ -32784,19 +32784,19 @@
         <v>156</v>
       </c>
       <c r="E34" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="F34" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="G34" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="H34" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="I34" t="n">
-        <v>2.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="35">
@@ -32820,10 +32820,10 @@
         <v>3.0</v>
       </c>
       <c r="H35" t="s">
-        <v>108</v>
+        <v>88</v>
       </c>
       <c r="I35" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="36">
@@ -32847,10 +32847,10 @@
         <v>3.0</v>
       </c>
       <c r="H36" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="I36" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="37">
@@ -32874,7 +32874,7 @@
         <v>3.0</v>
       </c>
       <c r="H37" t="s">
-        <v>109</v>
+        <v>92</v>
       </c>
       <c r="I37" t="n">
         <v>3.0</v>
@@ -32892,19 +32892,19 @@
         <v>156</v>
       </c>
       <c r="E38" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="F38" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="G38" t="n">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="H38" t="s">
-        <v>95</v>
+        <v>109</v>
       </c>
       <c r="I38" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="39">
@@ -32913,22 +32913,22 @@
       </c>
       <c r="B39"/>
       <c r="C39" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D39" t="s">
         <v>156</v>
       </c>
       <c r="E39" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="F39" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="G39" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
       <c r="H39" t="s">
-        <v>104</v>
+        <v>8</v>
       </c>
       <c r="I39" t="n">
         <v>1.0</v>
@@ -32955,10 +32955,10 @@
         <v>1.0</v>
       </c>
       <c r="H40" t="s">
-        <v>8</v>
+        <v>41</v>
       </c>
       <c r="I40" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="41">
@@ -32982,10 +32982,10 @@
         <v>1.0</v>
       </c>
       <c r="H41" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="I41" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="42">
@@ -33009,10 +33009,10 @@
         <v>1.0</v>
       </c>
       <c r="H42" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="I42" t="n">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="43">
@@ -33036,10 +33036,10 @@
         <v>1.0</v>
       </c>
       <c r="H43" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="I43" t="n">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="44">
@@ -33054,19 +33054,19 @@
         <v>156</v>
       </c>
       <c r="E44" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="F44" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="G44" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="H44" t="s">
+        <v>57</v>
+      </c>
+      <c r="I44" t="n">
         <v>1.0</v>
-      </c>
-      <c r="H44" t="s">
-        <v>53</v>
-      </c>
-      <c r="I44" t="n">
-        <v>5.0</v>
       </c>
     </row>
     <row r="45">
@@ -33090,10 +33090,10 @@
         <v>2.0</v>
       </c>
       <c r="H45" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="I45" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="46">
@@ -33117,10 +33117,10 @@
         <v>2.0</v>
       </c>
       <c r="H46" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="I46" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="47">
@@ -33144,10 +33144,10 @@
         <v>2.0</v>
       </c>
       <c r="H47" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="I47" t="n">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="48">
@@ -33171,10 +33171,10 @@
         <v>2.0</v>
       </c>
       <c r="H48" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="I48" t="n">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="49">
@@ -33198,10 +33198,10 @@
         <v>2.0</v>
       </c>
       <c r="H49" t="s">
-        <v>73</v>
+        <v>104</v>
       </c>
       <c r="I49" t="n">
-        <v>5.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="50">
@@ -33225,10 +33225,10 @@
         <v>2.0</v>
       </c>
       <c r="H50" t="s">
-        <v>99</v>
+        <v>78</v>
       </c>
       <c r="I50" t="n">
-        <v>6.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="51">
@@ -33243,19 +33243,19 @@
         <v>156</v>
       </c>
       <c r="E51" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="F51" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="G51" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="H51" t="s">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="I51" t="n">
-        <v>7.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="52">
@@ -33279,10 +33279,10 @@
         <v>3.0</v>
       </c>
       <c r="H52" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="I52" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="53">
@@ -33306,10 +33306,10 @@
         <v>3.0</v>
       </c>
       <c r="H53" t="s">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="I53" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="54">
@@ -33333,10 +33333,10 @@
         <v>3.0</v>
       </c>
       <c r="H54" t="s">
-        <v>91</v>
+        <v>100</v>
       </c>
       <c r="I54" t="n">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="55">
@@ -33360,7 +33360,7 @@
         <v>4.0</v>
       </c>
       <c r="H55" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="I55" t="n">
         <v>1.0</v>
@@ -33657,7 +33657,7 @@
         <v>2.0</v>
       </c>
       <c r="H66" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="I66" t="n">
         <v>6.0</v>
@@ -33711,7 +33711,7 @@
         <v>3.0</v>
       </c>
       <c r="H68" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="I68" t="n">
         <v>1.0</v>
@@ -33765,7 +33765,7 @@
         <v>3.0</v>
       </c>
       <c r="H70" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="I70" t="n">
         <v>3.0</v>
@@ -33783,19 +33783,19 @@
         <v>156</v>
       </c>
       <c r="E71" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="F71" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="G71" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="H71" t="s">
+        <v>100</v>
+      </c>
+      <c r="I71" t="n">
         <v>4.0</v>
-      </c>
-      <c r="H71" t="s">
-        <v>104</v>
-      </c>
-      <c r="I71" t="n">
-        <v>1.0</v>
       </c>
     </row>
     <row r="72">
@@ -33804,22 +33804,22 @@
       </c>
       <c r="B72"/>
       <c r="C72" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D72" t="s">
         <v>156</v>
       </c>
       <c r="E72" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
       <c r="F72" t="s">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="G72" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
       <c r="H72" t="s">
-        <v>8</v>
+        <v>109</v>
       </c>
       <c r="I72" t="n">
         <v>1.0</v>
@@ -33846,10 +33846,10 @@
         <v>1.0</v>
       </c>
       <c r="H73" t="s">
-        <v>41</v>
+        <v>8</v>
       </c>
       <c r="I73" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="74">
@@ -33873,10 +33873,10 @@
         <v>1.0</v>
       </c>
       <c r="H74" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="I74" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="75">
@@ -33900,10 +33900,10 @@
         <v>1.0</v>
       </c>
       <c r="H75" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="I75" t="n">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="76">
@@ -33927,10 +33927,10 @@
         <v>1.0</v>
       </c>
       <c r="H76" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="I76" t="n">
-        <v>5.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="77">
@@ -33945,19 +33945,19 @@
         <v>156</v>
       </c>
       <c r="E77" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="F77" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="G77" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="H77" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="I77" t="n">
-        <v>1.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="78">
@@ -33981,10 +33981,10 @@
         <v>2.0</v>
       </c>
       <c r="H78" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="I78" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="79">
@@ -34008,10 +34008,10 @@
         <v>2.0</v>
       </c>
       <c r="H79" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="I79" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="80">
@@ -34035,10 +34035,10 @@
         <v>2.0</v>
       </c>
       <c r="H80" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="I80" t="n">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="81">
@@ -34062,10 +34062,10 @@
         <v>2.0</v>
       </c>
       <c r="H81" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="I81" t="n">
-        <v>5.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="82">
@@ -34089,10 +34089,10 @@
         <v>2.0</v>
       </c>
       <c r="H82" t="s">
-        <v>99</v>
+        <v>73</v>
       </c>
       <c r="I82" t="n">
-        <v>6.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="83">
@@ -34116,10 +34116,10 @@
         <v>2.0</v>
       </c>
       <c r="H83" t="s">
-        <v>78</v>
+        <v>104</v>
       </c>
       <c r="I83" t="n">
-        <v>7.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="84">
@@ -34134,19 +34134,19 @@
         <v>156</v>
       </c>
       <c r="E84" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="F84" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="G84" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="H84" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="I84" t="n">
-        <v>1.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="85">
@@ -34170,10 +34170,10 @@
         <v>3.0</v>
       </c>
       <c r="H85" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="I85" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="86">
@@ -34197,10 +34197,10 @@
         <v>3.0</v>
       </c>
       <c r="H86" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="I86" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="87">
@@ -34224,10 +34224,10 @@
         <v>3.0</v>
       </c>
       <c r="H87" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="I87" t="n">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="88">
@@ -34251,7 +34251,7 @@
         <v>4.0</v>
       </c>
       <c r="H88" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="I88" t="n">
         <v>1.0</v>
@@ -34548,7 +34548,7 @@
         <v>2.0</v>
       </c>
       <c r="H99" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="I99" t="n">
         <v>6.0</v>
@@ -34602,7 +34602,7 @@
         <v>3.0</v>
       </c>
       <c r="H101" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="I101" t="n">
         <v>1.0</v>
@@ -34656,7 +34656,7 @@
         <v>3.0</v>
       </c>
       <c r="H103" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="I103" t="n">
         <v>3.0</v>
@@ -34683,7 +34683,7 @@
         <v>4.0</v>
       </c>
       <c r="H104" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="I104" t="n">
         <v>1.0</v>
@@ -34980,7 +34980,7 @@
         <v>2.0</v>
       </c>
       <c r="H115" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="I115" t="n">
         <v>6.0</v>
@@ -35034,7 +35034,7 @@
         <v>3.0</v>
       </c>
       <c r="H117" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="I117" t="n">
         <v>1.0</v>
@@ -35088,7 +35088,7 @@
         <v>3.0</v>
       </c>
       <c r="H119" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="I119" t="n">
         <v>3.0</v>
@@ -35115,7 +35115,7 @@
         <v>3.0</v>
       </c>
       <c r="H120" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="I120" t="n">
         <v>4.0</v>
@@ -35142,7 +35142,7 @@
         <v>4.0</v>
       </c>
       <c r="H121" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="I121" t="n">
         <v>1.0</v>
@@ -35439,7 +35439,7 @@
         <v>2.0</v>
       </c>
       <c r="H132" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="I132" t="n">
         <v>6.0</v>
@@ -35493,7 +35493,7 @@
         <v>3.0</v>
       </c>
       <c r="H134" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="I134" t="n">
         <v>1.0</v>
@@ -35547,7 +35547,7 @@
         <v>3.0</v>
       </c>
       <c r="H136" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="I136" t="n">
         <v>3.0</v>
@@ -35574,7 +35574,7 @@
         <v>4.0</v>
       </c>
       <c r="H137" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="I137" t="n">
         <v>1.0</v>
